--- a/research/traditional_assets/database/data/new_zealand/new_zealand_paper_forest_products.xlsx
+++ b/research/traditional_assets/database/data/new_zealand/new_zealand_paper_forest_products.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="nzse_arb" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,22 +590,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>0.1686507936507937</v>
+        <v>0.1680129240710824</v>
       </c>
       <c r="H2">
-        <v>0.1686507936507937</v>
+        <v>0.1680129240710824</v>
       </c>
       <c r="I2">
-        <v>-0.03571428571428572</v>
+        <v>0.06785137318255251</v>
       </c>
       <c r="J2">
-        <v>-0.03571428571428572</v>
+        <v>0.03392568659127625</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>-0.01615508885298869</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -611,83 +613,89 @@
       <c r="N2">
         <v>0</v>
       </c>
+      <c r="O2">
+        <v>-0</v>
+      </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
         <v>0</v>
       </c>
+      <c r="R2">
+        <v>-0</v>
+      </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>8.4</v>
+        <v>4.3</v>
       </c>
       <c r="V2">
-        <v>0.1145975443383356</v>
+        <v>0.07933579335793357</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>-0.006675567423230974</v>
       </c>
       <c r="X2">
-        <v>0.09709829775006033</v>
+        <v>0.08098856527096454</v>
       </c>
       <c r="Y2">
-        <v>-0.09709829775006033</v>
+        <v>-0.08766413269419551</v>
       </c>
       <c r="Z2">
-        <v>0.2746594005449591</v>
+        <v>0.3594657375145179</v>
       </c>
       <c r="AA2">
-        <v>-0.009809264305177113</v>
+        <v>0.01219512195121951</v>
       </c>
       <c r="AB2">
-        <v>0.0800863134013393</v>
+        <v>0.06425468679185342</v>
       </c>
       <c r="AC2">
-        <v>-0.08989557770651642</v>
+        <v>-0.05205956484063391</v>
       </c>
       <c r="AD2">
-        <v>30.8</v>
+        <v>28.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>30.8</v>
+        <v>28.5</v>
       </c>
       <c r="AG2">
-        <v>22.4</v>
+        <v>24.2</v>
       </c>
       <c r="AH2">
-        <v>0.2958693563880884</v>
+        <v>0.3446191051995163</v>
       </c>
       <c r="AI2">
-        <v>0.1705426356589147</v>
+        <v>0.1609260304912479</v>
       </c>
       <c r="AJ2">
-        <v>0.2340647857889237</v>
+        <v>0.3086734693877551</v>
       </c>
       <c r="AK2">
-        <v>0.1300813008130081</v>
+        <v>0.1400462962962963</v>
       </c>
       <c r="AL2">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="AM2">
         <v>0.1</v>
       </c>
       <c r="AN2">
-        <v>3.89873417721519</v>
+        <v>2.035714285714286</v>
       </c>
       <c r="AO2">
-        <v>-18</v>
+        <v>10.5</v>
       </c>
       <c r="AP2">
-        <v>2.835443037974683</v>
+        <v>1.728571428571428</v>
       </c>
       <c r="AQ2">
-        <v>-18</v>
+        <v>41.99999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -707,22 +715,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.1686507936507937</v>
+        <v>0.1680129240710824</v>
       </c>
       <c r="H3">
-        <v>0.1686507936507937</v>
+        <v>0.1680129240710824</v>
       </c>
       <c r="I3">
-        <v>-0.03571428571428572</v>
+        <v>0.06785137318255251</v>
       </c>
       <c r="J3">
-        <v>-0.03571428571428572</v>
+        <v>0.03392568659127625</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>-0.01615508885298869</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -730,83 +738,8861 @@
       <c r="N3">
         <v>-0</v>
       </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
       <c r="P3">
         <v>-0</v>
       </c>
       <c r="Q3">
         <v>-0</v>
       </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>8.4</v>
+        <v>4.3</v>
       </c>
       <c r="V3">
-        <v>0.1145975443383356</v>
+        <v>0.07933579335793357</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>-0.006675567423230974</v>
       </c>
       <c r="X3">
-        <v>0.09709829775006033</v>
+        <v>0.08098856527096454</v>
       </c>
       <c r="Y3">
-        <v>-0.09709829775006033</v>
+        <v>-0.08766413269419551</v>
       </c>
       <c r="Z3">
-        <v>0.2746594005449591</v>
+        <v>0.3594657375145179</v>
       </c>
       <c r="AA3">
-        <v>-0.009809264305177113</v>
+        <v>0.01219512195121951</v>
       </c>
       <c r="AB3">
-        <v>0.0800863134013393</v>
+        <v>0.06425468679185342</v>
       </c>
       <c r="AC3">
-        <v>-0.08989557770651642</v>
+        <v>-0.05205956484063391</v>
       </c>
       <c r="AD3">
-        <v>30.8</v>
+        <v>28.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>30.8</v>
+        <v>28.5</v>
       </c>
       <c r="AG3">
-        <v>22.4</v>
+        <v>24.2</v>
       </c>
       <c r="AH3">
-        <v>0.2958693563880884</v>
+        <v>0.3446191051995163</v>
       </c>
       <c r="AI3">
-        <v>0.1705426356589147</v>
+        <v>0.1609260304912479</v>
       </c>
       <c r="AJ3">
-        <v>0.2340647857889237</v>
+        <v>0.3086734693877551</v>
       </c>
       <c r="AK3">
-        <v>0.1300813008130081</v>
+        <v>0.1400462962962963</v>
       </c>
       <c r="AL3">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="AM3">
         <v>0.1</v>
       </c>
       <c r="AN3">
-        <v>3.89873417721519</v>
+        <v>2.035714285714286</v>
       </c>
       <c r="AO3">
-        <v>-18</v>
+        <v>10.5</v>
       </c>
       <c r="AP3">
-        <v>2.835443037974683</v>
+        <v>1.728571428571428</v>
       </c>
       <c r="AQ3">
-        <v>-18</v>
+        <v>41.99999999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ArborGen Holdings Limited (NZSE:ARB)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NZSE:ARB</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Paper/Forest Products</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>15.75</v>
+      </c>
+      <c r="F2">
+        <v>4.53527178048075</v>
+      </c>
+      <c r="G2">
+        <v>2.03571428571429</v>
+      </c>
+      <c r="H2">
+        <v>1.94935714285714</v>
+      </c>
+      <c r="I2">
+        <v>0.344619105199516</v>
+      </c>
+      <c r="J2">
+        <v>0.33</v>
+      </c>
+      <c r="K2">
+        <v>54.2</v>
+      </c>
+      <c r="L2">
+        <v>54.3865351143543</v>
+      </c>
+      <c r="M2">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="N2">
+        <v>77.3775351143543</v>
+      </c>
+      <c r="O2">
+        <v>28.5</v>
+      </c>
+      <c r="P2">
+        <v>27.291</v>
+      </c>
+      <c r="Q2">
+        <v>0.06425468679185339</v>
+      </c>
+      <c r="R2">
+        <v>0.0658646864631165</v>
+      </c>
+      <c r="S2">
+        <v>0.03243096</v>
+      </c>
+      <c r="T2">
+        <v>0.036648</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.0809885652709645</v>
+      </c>
+      <c r="X2">
+        <v>0.08025499472106939</v>
+      </c>
+      <c r="Y2">
+        <v>0.917142723281838</v>
+      </c>
+      <c r="Z2">
+        <v>0.901195537414553</v>
+      </c>
+      <c r="AA2">
+        <v>28.5</v>
+      </c>
+      <c r="AB2">
+        <v>0.045043</v>
+      </c>
+      <c r="AC2">
+        <v>15.75</v>
+      </c>
+      <c r="AD2">
+        <v>28.5</v>
+      </c>
+      <c r="AE2">
+        <v>0.4</v>
+      </c>
+      <c r="AF2">
+        <v>7.7</v>
+      </c>
+      <c r="AG2">
+        <v>14</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>54.2</v>
+      </c>
+      <c r="AK2">
+        <v>0.046</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.28</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>2.100000000000001</v>
+      </c>
+      <c r="AR2">
+        <v>0.4</v>
+      </c>
+      <c r="AS2">
+        <v>28.5</v>
+      </c>
+      <c r="AT2">
+        <v>4.3</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.06940251924098338</v>
+      </c>
+      <c r="C2">
+        <v>79.52183773995893</v>
+      </c>
+      <c r="D2">
+        <v>75.22183773995893</v>
+      </c>
+      <c r="E2">
+        <v>-28.5</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>4.3</v>
+      </c>
+      <c r="H2">
+        <v>54.2</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>14</v>
+      </c>
+      <c r="K2">
+        <v>7.7</v>
+      </c>
+      <c r="L2">
+        <v>6.3</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>6.3</v>
+      </c>
+      <c r="O2">
+        <v>1.764</v>
+      </c>
+      <c r="P2">
+        <v>4.536</v>
+      </c>
+      <c r="Q2">
+        <v>12.236</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.06940251924098338</v>
+      </c>
+      <c r="T2">
+        <v>0.6652721574126822</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.28</v>
+      </c>
+      <c r="W2">
+        <v>0.032184</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.06925067218710863</v>
+      </c>
+      <c r="C3">
+        <v>78.78489226297503</v>
+      </c>
+      <c r="D3">
+        <v>75.31189226297504</v>
+      </c>
+      <c r="E3">
+        <v>-27.673</v>
+      </c>
+      <c r="F3">
+        <v>0.8270000000000001</v>
+      </c>
+      <c r="G3">
+        <v>4.3</v>
+      </c>
+      <c r="H3">
+        <v>54.2</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>14</v>
+      </c>
+      <c r="K3">
+        <v>7.7</v>
+      </c>
+      <c r="L3">
+        <v>6.3</v>
+      </c>
+      <c r="M3">
+        <v>0.0369669</v>
+      </c>
+      <c r="N3">
+        <v>6.263033099999999</v>
+      </c>
+      <c r="O3">
+        <v>1.753649268</v>
+      </c>
+      <c r="P3">
+        <v>4.509383831999999</v>
+      </c>
+      <c r="Q3">
+        <v>12.209383832</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.06962508301728144</v>
+      </c>
+      <c r="T3">
+        <v>0.6701105003756835</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.28</v>
+      </c>
+      <c r="W3">
+        <v>0.032184</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>170.4227295228975</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.06909882513323387</v>
+      </c>
+      <c r="C4">
+        <v>78.04816266845177</v>
+      </c>
+      <c r="D4">
+        <v>75.40216266845177</v>
+      </c>
+      <c r="E4">
+        <v>-26.846</v>
+      </c>
+      <c r="F4">
+        <v>1.654</v>
+      </c>
+      <c r="G4">
+        <v>4.3</v>
+      </c>
+      <c r="H4">
+        <v>54.2</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>14</v>
+      </c>
+      <c r="K4">
+        <v>7.7</v>
+      </c>
+      <c r="L4">
+        <v>6.3</v>
+      </c>
+      <c r="M4">
+        <v>0.07393380000000001</v>
+      </c>
+      <c r="N4">
+        <v>6.2260662</v>
+      </c>
+      <c r="O4">
+        <v>1.743298536</v>
+      </c>
+      <c r="P4">
+        <v>4.482767664</v>
+      </c>
+      <c r="Q4">
+        <v>12.182767664</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.06985218891146314</v>
+      </c>
+      <c r="T4">
+        <v>0.6750475850318073</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.28</v>
+      </c>
+      <c r="W4">
+        <v>0.032184</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>85.21136476144875</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.06894697807935911</v>
+      </c>
+      <c r="C5">
+        <v>77.31164973360436</v>
+      </c>
+      <c r="D5">
+        <v>75.49264973360435</v>
+      </c>
+      <c r="E5">
+        <v>-26.019</v>
+      </c>
+      <c r="F5">
+        <v>2.481</v>
+      </c>
+      <c r="G5">
+        <v>4.3</v>
+      </c>
+      <c r="H5">
+        <v>54.2</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>14</v>
+      </c>
+      <c r="K5">
+        <v>7.7</v>
+      </c>
+      <c r="L5">
+        <v>6.3</v>
+      </c>
+      <c r="M5">
+        <v>0.1109007</v>
+      </c>
+      <c r="N5">
+        <v>6.1890993</v>
+      </c>
+      <c r="O5">
+        <v>1.732947804</v>
+      </c>
+      <c r="P5">
+        <v>4.456151495999999</v>
+      </c>
+      <c r="Q5">
+        <v>12.156151496</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.07008397740140115</v>
+      </c>
+      <c r="T5">
+        <v>0.6800864652478512</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.28</v>
+      </c>
+      <c r="W5">
+        <v>0.032184</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>56.8075765076325</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.06879513102548436</v>
+      </c>
+      <c r="C6">
+        <v>76.57535423938336</v>
+      </c>
+      <c r="D6">
+        <v>75.58335423938337</v>
+      </c>
+      <c r="E6">
+        <v>-25.192</v>
+      </c>
+      <c r="F6">
+        <v>3.308</v>
+      </c>
+      <c r="G6">
+        <v>4.3</v>
+      </c>
+      <c r="H6">
+        <v>54.2</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>14</v>
+      </c>
+      <c r="K6">
+        <v>7.7</v>
+      </c>
+      <c r="L6">
+        <v>6.3</v>
+      </c>
+      <c r="M6">
+        <v>0.1478676</v>
+      </c>
+      <c r="N6">
+        <v>6.1521324</v>
+      </c>
+      <c r="O6">
+        <v>1.722597072</v>
+      </c>
+      <c r="P6">
+        <v>4.429535328</v>
+      </c>
+      <c r="Q6">
+        <v>12.129535328</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.07032059481821287</v>
+      </c>
+      <c r="T6">
+        <v>0.6852303221350626</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.28</v>
+      </c>
+      <c r="W6">
+        <v>0.032184</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>42.60568238072437</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.06864328397160961</v>
+      </c>
+      <c r="C7">
+        <v>75.8392769704971</v>
+      </c>
+      <c r="D7">
+        <v>75.6742769704971</v>
+      </c>
+      <c r="E7">
+        <v>-24.365</v>
+      </c>
+      <c r="F7">
+        <v>4.135000000000001</v>
+      </c>
+      <c r="G7">
+        <v>4.3</v>
+      </c>
+      <c r="H7">
+        <v>54.2</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>14</v>
+      </c>
+      <c r="K7">
+        <v>7.7</v>
+      </c>
+      <c r="L7">
+        <v>6.3</v>
+      </c>
+      <c r="M7">
+        <v>0.1848345</v>
+      </c>
+      <c r="N7">
+        <v>6.1151655</v>
+      </c>
+      <c r="O7">
+        <v>1.71224634</v>
+      </c>
+      <c r="P7">
+        <v>4.40291916</v>
+      </c>
+      <c r="Q7">
+        <v>12.10291916</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.07056219365432591</v>
+      </c>
+      <c r="T7">
+        <v>0.6904824707462154</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.28</v>
+      </c>
+      <c r="W7">
+        <v>0.032184</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>34.08454590457949</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.06849143691773485</v>
+      </c>
+      <c r="C8">
+        <v>75.1034187154343</v>
+      </c>
+      <c r="D8">
+        <v>75.76541871543431</v>
+      </c>
+      <c r="E8">
+        <v>-23.538</v>
+      </c>
+      <c r="F8">
+        <v>4.962</v>
+      </c>
+      <c r="G8">
+        <v>4.3</v>
+      </c>
+      <c r="H8">
+        <v>54.2</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>14</v>
+      </c>
+      <c r="K8">
+        <v>7.7</v>
+      </c>
+      <c r="L8">
+        <v>6.3</v>
+      </c>
+      <c r="M8">
+        <v>0.2218014</v>
+      </c>
+      <c r="N8">
+        <v>6.078198599999999</v>
+      </c>
+      <c r="O8">
+        <v>1.701895608</v>
+      </c>
+      <c r="P8">
+        <v>4.376302991999999</v>
+      </c>
+      <c r="Q8">
+        <v>12.076302992</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.07080893289120729</v>
+      </c>
+      <c r="T8">
+        <v>0.6958463672001587</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.28</v>
+      </c>
+      <c r="W8">
+        <v>0.032184</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>28.40378825381625</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.0683395898638601</v>
+      </c>
+      <c r="C9">
+        <v>74.36778026648686</v>
+      </c>
+      <c r="D9">
+        <v>75.85678026648687</v>
+      </c>
+      <c r="E9">
+        <v>-22.711</v>
+      </c>
+      <c r="F9">
+        <v>5.789000000000001</v>
+      </c>
+      <c r="G9">
+        <v>4.3</v>
+      </c>
+      <c r="H9">
+        <v>54.2</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>14</v>
+      </c>
+      <c r="K9">
+        <v>7.7</v>
+      </c>
+      <c r="L9">
+        <v>6.3</v>
+      </c>
+      <c r="M9">
+        <v>0.2587683000000001</v>
+      </c>
+      <c r="N9">
+        <v>6.0412317</v>
+      </c>
+      <c r="O9">
+        <v>1.691544876</v>
+      </c>
+      <c r="P9">
+        <v>4.349686824</v>
+      </c>
+      <c r="Q9">
+        <v>12.049686824</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.07106097834823667</v>
+      </c>
+      <c r="T9">
+        <v>0.7013256162660146</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.28</v>
+      </c>
+      <c r="W9">
+        <v>0.032184</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>24.34610421755678</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.06818774280998535</v>
+      </c>
+      <c r="C10">
+        <v>73.63236241977282</v>
+      </c>
+      <c r="D10">
+        <v>75.94836241977282</v>
+      </c>
+      <c r="E10">
+        <v>-21.884</v>
+      </c>
+      <c r="F10">
+        <v>6.616000000000001</v>
+      </c>
+      <c r="G10">
+        <v>4.3</v>
+      </c>
+      <c r="H10">
+        <v>54.2</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>14</v>
+      </c>
+      <c r="K10">
+        <v>7.7</v>
+      </c>
+      <c r="L10">
+        <v>6.3</v>
+      </c>
+      <c r="M10">
+        <v>0.2957352</v>
+      </c>
+      <c r="N10">
+        <v>6.0042648</v>
+      </c>
+      <c r="O10">
+        <v>1.681194144</v>
+      </c>
+      <c r="P10">
+        <v>4.323070656</v>
+      </c>
+      <c r="Q10">
+        <v>12.023070656</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.07131850305433191</v>
+      </c>
+      <c r="T10">
+        <v>0.7069239794419979</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.28</v>
+      </c>
+      <c r="W10">
+        <v>0.032184</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>21.30284119036218</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.0680358957561106</v>
+      </c>
+      <c r="C11">
+        <v>72.89716597525951</v>
+      </c>
+      <c r="D11">
+        <v>76.04016597525951</v>
+      </c>
+      <c r="E11">
+        <v>-21.057</v>
+      </c>
+      <c r="F11">
+        <v>7.443</v>
+      </c>
+      <c r="G11">
+        <v>4.3</v>
+      </c>
+      <c r="H11">
+        <v>54.2</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>14</v>
+      </c>
+      <c r="K11">
+        <v>7.7</v>
+      </c>
+      <c r="L11">
+        <v>6.3</v>
+      </c>
+      <c r="M11">
+        <v>0.3327021</v>
+      </c>
+      <c r="N11">
+        <v>5.9672979</v>
+      </c>
+      <c r="O11">
+        <v>1.670843412</v>
+      </c>
+      <c r="P11">
+        <v>4.296454488</v>
+      </c>
+      <c r="Q11">
+        <v>11.996454488</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.07158168764407757</v>
+      </c>
+      <c r="T11">
+        <v>0.712645383566904</v>
+      </c>
+      <c r="U11">
+        <v>0.0447</v>
+      </c>
+      <c r="V11">
+        <v>0.28</v>
+      </c>
+      <c r="W11">
+        <v>0.032184</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>18.9358588358775</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.06788404870223586</v>
+      </c>
+      <c r="C12">
+        <v>72.16219173678682</v>
+      </c>
+      <c r="D12">
+        <v>76.13219173678682</v>
+      </c>
+      <c r="E12">
+        <v>-20.23</v>
+      </c>
+      <c r="F12">
+        <v>8.270000000000001</v>
+      </c>
+      <c r="G12">
+        <v>4.3</v>
+      </c>
+      <c r="H12">
+        <v>54.2</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>14</v>
+      </c>
+      <c r="K12">
+        <v>7.7</v>
+      </c>
+      <c r="L12">
+        <v>6.3</v>
+      </c>
+      <c r="M12">
+        <v>0.3696690000000001</v>
+      </c>
+      <c r="N12">
+        <v>5.930331</v>
+      </c>
+      <c r="O12">
+        <v>1.66049268</v>
+      </c>
+      <c r="P12">
+        <v>4.26983832</v>
+      </c>
+      <c r="Q12">
+        <v>11.96983832</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.07185072078026206</v>
+      </c>
+      <c r="T12">
+        <v>0.7184939300056968</v>
+      </c>
+      <c r="U12">
+        <v>0.0447</v>
+      </c>
+      <c r="V12">
+        <v>0.28</v>
+      </c>
+      <c r="W12">
+        <v>0.032184</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>17.04227295228975</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.06773220164836109</v>
+      </c>
+      <c r="C13">
+        <v>71.42744051209066</v>
+      </c>
+      <c r="D13">
+        <v>76.22444051209065</v>
+      </c>
+      <c r="E13">
+        <v>-19.403</v>
+      </c>
+      <c r="F13">
+        <v>9.097</v>
+      </c>
+      <c r="G13">
+        <v>4.3</v>
+      </c>
+      <c r="H13">
+        <v>54.2</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>14</v>
+      </c>
+      <c r="K13">
+        <v>7.7</v>
+      </c>
+      <c r="L13">
+        <v>6.3</v>
+      </c>
+      <c r="M13">
+        <v>0.4066359</v>
+      </c>
+      <c r="N13">
+        <v>5.893364099999999</v>
+      </c>
+      <c r="O13">
+        <v>1.650141948</v>
+      </c>
+      <c r="P13">
+        <v>4.243222152</v>
+      </c>
+      <c r="Q13">
+        <v>11.943222152</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.07212579960490011</v>
+      </c>
+      <c r="T13">
+        <v>0.7244739044543501</v>
+      </c>
+      <c r="U13">
+        <v>0.0447</v>
+      </c>
+      <c r="V13">
+        <v>0.28</v>
+      </c>
+      <c r="W13">
+        <v>0.032184</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>15.4929754111725</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.06758035459448634</v>
+      </c>
+      <c r="C14">
+        <v>70.6929131128266</v>
+      </c>
+      <c r="D14">
+        <v>76.3169131128266</v>
+      </c>
+      <c r="E14">
+        <v>-18.576</v>
+      </c>
+      <c r="F14">
+        <v>9.923999999999999</v>
+      </c>
+      <c r="G14">
+        <v>4.3</v>
+      </c>
+      <c r="H14">
+        <v>54.2</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>14</v>
+      </c>
+      <c r="K14">
+        <v>7.7</v>
+      </c>
+      <c r="L14">
+        <v>6.3</v>
+      </c>
+      <c r="M14">
+        <v>0.4436028</v>
+      </c>
+      <c r="N14">
+        <v>5.8563972</v>
+      </c>
+      <c r="O14">
+        <v>1.639791216</v>
+      </c>
+      <c r="P14">
+        <v>4.216605984</v>
+      </c>
+      <c r="Q14">
+        <v>11.916605984</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.0724071302210072</v>
+      </c>
+      <c r="T14">
+        <v>0.7305897874132</v>
+      </c>
+      <c r="U14">
+        <v>0.0447</v>
+      </c>
+      <c r="V14">
+        <v>0.28</v>
+      </c>
+      <c r="W14">
+        <v>0.032184</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>14.20189412690813</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.06742850754061158</v>
+      </c>
+      <c r="C15">
+        <v>69.95861035459366</v>
+      </c>
+      <c r="D15">
+        <v>76.40961035459367</v>
+      </c>
+      <c r="E15">
+        <v>-17.749</v>
+      </c>
+      <c r="F15">
+        <v>10.751</v>
+      </c>
+      <c r="G15">
+        <v>4.3</v>
+      </c>
+      <c r="H15">
+        <v>54.2</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>14</v>
+      </c>
+      <c r="K15">
+        <v>7.7</v>
+      </c>
+      <c r="L15">
+        <v>6.3</v>
+      </c>
+      <c r="M15">
+        <v>0.4805697000000001</v>
+      </c>
+      <c r="N15">
+        <v>5.8194303</v>
+      </c>
+      <c r="O15">
+        <v>1.629440484</v>
+      </c>
+      <c r="P15">
+        <v>4.189989816</v>
+      </c>
+      <c r="Q15">
+        <v>11.889989816</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.07269492820759953</v>
+      </c>
+      <c r="T15">
+        <v>0.7368462653825983</v>
+      </c>
+      <c r="U15">
+        <v>0.0447</v>
+      </c>
+      <c r="V15">
+        <v>0.28</v>
+      </c>
+      <c r="W15">
+        <v>0.032184</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>13.10944073253057</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.06738754048673684</v>
+      </c>
+      <c r="C16">
+        <v>69.1566578730329</v>
+      </c>
+      <c r="D16">
+        <v>76.4346578730329</v>
+      </c>
+      <c r="E16">
+        <v>-16.922</v>
+      </c>
+      <c r="F16">
+        <v>11.578</v>
+      </c>
+      <c r="G16">
+        <v>4.3</v>
+      </c>
+      <c r="H16">
+        <v>54.2</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>14</v>
+      </c>
+      <c r="K16">
+        <v>7.7</v>
+      </c>
+      <c r="L16">
+        <v>6.3</v>
+      </c>
+      <c r="M16">
+        <v>0.5302724000000001</v>
+      </c>
+      <c r="N16">
+        <v>5.7697276</v>
+      </c>
+      <c r="O16">
+        <v>1.615523728</v>
+      </c>
+      <c r="P16">
+        <v>4.154203871999999</v>
+      </c>
+      <c r="Q16">
+        <v>11.854203872</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.07298941917062422</v>
+      </c>
+      <c r="T16">
+        <v>0.743248242839657</v>
+      </c>
+      <c r="U16">
+        <v>0.0458</v>
+      </c>
+      <c r="V16">
+        <v>0.28</v>
+      </c>
+      <c r="W16">
+        <v>0.032976</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>11.88068622843655</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.06724361343286207</v>
+      </c>
+      <c r="C17">
+        <v>68.41778613324654</v>
+      </c>
+      <c r="D17">
+        <v>76.52278613324654</v>
+      </c>
+      <c r="E17">
+        <v>-16.095</v>
+      </c>
+      <c r="F17">
+        <v>12.405</v>
+      </c>
+      <c r="G17">
+        <v>4.3</v>
+      </c>
+      <c r="H17">
+        <v>54.2</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>14</v>
+      </c>
+      <c r="K17">
+        <v>7.7</v>
+      </c>
+      <c r="L17">
+        <v>6.3</v>
+      </c>
+      <c r="M17">
+        <v>0.568149</v>
+      </c>
+      <c r="N17">
+        <v>5.731851</v>
+      </c>
+      <c r="O17">
+        <v>1.60491828</v>
+      </c>
+      <c r="P17">
+        <v>4.126932719999999</v>
+      </c>
+      <c r="Q17">
+        <v>11.82693272</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.07329083933277891</v>
+      </c>
+      <c r="T17">
+        <v>0.7498008550604112</v>
+      </c>
+      <c r="U17">
+        <v>0.0458</v>
+      </c>
+      <c r="V17">
+        <v>0.28</v>
+      </c>
+      <c r="W17">
+        <v>0.032976</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>11.08864047987412</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.06709968637898733</v>
+      </c>
+      <c r="C18">
+        <v>67.67911784973479</v>
+      </c>
+      <c r="D18">
+        <v>76.6111178497348</v>
+      </c>
+      <c r="E18">
+        <v>-15.268</v>
+      </c>
+      <c r="F18">
+        <v>13.232</v>
+      </c>
+      <c r="G18">
+        <v>4.3</v>
+      </c>
+      <c r="H18">
+        <v>54.2</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>14</v>
+      </c>
+      <c r="K18">
+        <v>7.7</v>
+      </c>
+      <c r="L18">
+        <v>6.3</v>
+      </c>
+      <c r="M18">
+        <v>0.6060256000000001</v>
+      </c>
+      <c r="N18">
+        <v>5.6939744</v>
+      </c>
+      <c r="O18">
+        <v>1.594312832</v>
+      </c>
+      <c r="P18">
+        <v>4.099661568</v>
+      </c>
+      <c r="Q18">
+        <v>11.799661568</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.07359943616546111</v>
+      </c>
+      <c r="T18">
+        <v>0.7565094818578501</v>
+      </c>
+      <c r="U18">
+        <v>0.0458</v>
+      </c>
+      <c r="V18">
+        <v>0.28</v>
+      </c>
+      <c r="W18">
+        <v>0.032976</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>10.39560044988198</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.06722503932511256</v>
+      </c>
+      <c r="C19">
+        <v>66.77517408963855</v>
+      </c>
+      <c r="D19">
+        <v>76.53417408963855</v>
+      </c>
+      <c r="E19">
+        <v>-14.441</v>
+      </c>
+      <c r="F19">
+        <v>14.059</v>
+      </c>
+      <c r="G19">
+        <v>4.3</v>
+      </c>
+      <c r="H19">
+        <v>54.2</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>14</v>
+      </c>
+      <c r="K19">
+        <v>7.7</v>
+      </c>
+      <c r="L19">
+        <v>6.3</v>
+      </c>
+      <c r="M19">
+        <v>0.6748320000000001</v>
+      </c>
+      <c r="N19">
+        <v>5.625168</v>
+      </c>
+      <c r="O19">
+        <v>1.57504704</v>
+      </c>
+      <c r="P19">
+        <v>4.050120959999999</v>
+      </c>
+      <c r="Q19">
+        <v>11.75012096</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.07391546906640069</v>
+      </c>
+      <c r="T19">
+        <v>0.7633797623130584</v>
+      </c>
+      <c r="U19">
+        <v>0.048</v>
+      </c>
+      <c r="V19">
+        <v>0.28</v>
+      </c>
+      <c r="W19">
+        <v>0.03456</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>9.335656874599898</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.06709695227123783</v>
+      </c>
+      <c r="C20">
+        <v>66.02679781541114</v>
+      </c>
+      <c r="D20">
+        <v>76.61279781541114</v>
+      </c>
+      <c r="E20">
+        <v>-13.614</v>
+      </c>
+      <c r="F20">
+        <v>14.886</v>
+      </c>
+      <c r="G20">
+        <v>4.3</v>
+      </c>
+      <c r="H20">
+        <v>54.2</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>14</v>
+      </c>
+      <c r="K20">
+        <v>7.7</v>
+      </c>
+      <c r="L20">
+        <v>6.3</v>
+      </c>
+      <c r="M20">
+        <v>0.7145279999999999</v>
+      </c>
+      <c r="N20">
+        <v>5.585472</v>
+      </c>
+      <c r="O20">
+        <v>1.56393216</v>
+      </c>
+      <c r="P20">
+        <v>4.02153984</v>
+      </c>
+      <c r="Q20">
+        <v>11.72153984</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.0742392100868754</v>
+      </c>
+      <c r="T20">
+        <v>0.7704176105842475</v>
+      </c>
+      <c r="U20">
+        <v>0.048</v>
+      </c>
+      <c r="V20">
+        <v>0.28</v>
+      </c>
+      <c r="W20">
+        <v>0.03456</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>8.817009270455461</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.06696886521736306</v>
+      </c>
+      <c r="C21">
+        <v>65.27858324795912</v>
+      </c>
+      <c r="D21">
+        <v>76.69158324795913</v>
+      </c>
+      <c r="E21">
+        <v>-12.787</v>
+      </c>
+      <c r="F21">
+        <v>15.713</v>
+      </c>
+      <c r="G21">
+        <v>4.3</v>
+      </c>
+      <c r="H21">
+        <v>54.2</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>14</v>
+      </c>
+      <c r="K21">
+        <v>7.7</v>
+      </c>
+      <c r="L21">
+        <v>6.3</v>
+      </c>
+      <c r="M21">
+        <v>0.7542240000000001</v>
+      </c>
+      <c r="N21">
+        <v>5.545776</v>
+      </c>
+      <c r="O21">
+        <v>1.55281728</v>
+      </c>
+      <c r="P21">
+        <v>3.99295872</v>
+      </c>
+      <c r="Q21">
+        <v>11.69295872</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.07457094471279391</v>
+      </c>
+      <c r="T21">
+        <v>0.7776292328868241</v>
+      </c>
+      <c r="U21">
+        <v>0.048</v>
+      </c>
+      <c r="V21">
+        <v>0.28</v>
+      </c>
+      <c r="W21">
+        <v>0.03456</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>8.352956150957805</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.06684077816348832</v>
+      </c>
+      <c r="C22">
+        <v>64.53053088667369</v>
+      </c>
+      <c r="D22">
+        <v>76.7705308866737</v>
+      </c>
+      <c r="E22">
+        <v>-11.96</v>
+      </c>
+      <c r="F22">
+        <v>16.54</v>
+      </c>
+      <c r="G22">
+        <v>4.3</v>
+      </c>
+      <c r="H22">
+        <v>54.2</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>14</v>
+      </c>
+      <c r="K22">
+        <v>7.7</v>
+      </c>
+      <c r="L22">
+        <v>6.3</v>
+      </c>
+      <c r="M22">
+        <v>0.7939200000000002</v>
+      </c>
+      <c r="N22">
+        <v>5.50608</v>
+      </c>
+      <c r="O22">
+        <v>1.5417024</v>
+      </c>
+      <c r="P22">
+        <v>3.9643776</v>
+      </c>
+      <c r="Q22">
+        <v>11.6643776</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.0749109727043604</v>
+      </c>
+      <c r="T22">
+        <v>0.7850211457469649</v>
+      </c>
+      <c r="U22">
+        <v>0.048</v>
+      </c>
+      <c r="V22">
+        <v>0.28</v>
+      </c>
+      <c r="W22">
+        <v>0.03456</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>7.935308343409914</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.06693949110961357</v>
+      </c>
+      <c r="C23">
+        <v>63.64267389851186</v>
+      </c>
+      <c r="D23">
+        <v>76.70967389851187</v>
+      </c>
+      <c r="E23">
+        <v>-11.133</v>
+      </c>
+      <c r="F23">
+        <v>17.367</v>
+      </c>
+      <c r="G23">
+        <v>4.3</v>
+      </c>
+      <c r="H23">
+        <v>54.2</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>14</v>
+      </c>
+      <c r="K23">
+        <v>7.7</v>
+      </c>
+      <c r="L23">
+        <v>6.3</v>
+      </c>
+      <c r="M23">
+        <v>0.8596665000000001</v>
+      </c>
+      <c r="N23">
+        <v>5.440333499999999</v>
+      </c>
+      <c r="O23">
+        <v>1.52329338</v>
+      </c>
+      <c r="P23">
+        <v>3.917040119999999</v>
+      </c>
+      <c r="Q23">
+        <v>11.61704012</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.07525960899951084</v>
+      </c>
+      <c r="T23">
+        <v>0.7926001956415398</v>
+      </c>
+      <c r="U23">
+        <v>0.0495</v>
+      </c>
+      <c r="V23">
+        <v>0.28</v>
+      </c>
+      <c r="W23">
+        <v>0.03564</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>7.328423289729213</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.06682220405573881</v>
+      </c>
+      <c r="C24">
+        <v>62.88799270563433</v>
+      </c>
+      <c r="D24">
+        <v>76.78199270563434</v>
+      </c>
+      <c r="E24">
+        <v>-10.306</v>
+      </c>
+      <c r="F24">
+        <v>18.194</v>
+      </c>
+      <c r="G24">
+        <v>4.3</v>
+      </c>
+      <c r="H24">
+        <v>54.2</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>14</v>
+      </c>
+      <c r="K24">
+        <v>7.7</v>
+      </c>
+      <c r="L24">
+        <v>6.3</v>
+      </c>
+      <c r="M24">
+        <v>0.900603</v>
+      </c>
+      <c r="N24">
+        <v>5.399397</v>
+      </c>
+      <c r="O24">
+        <v>1.51183116</v>
+      </c>
+      <c r="P24">
+        <v>3.88756584</v>
+      </c>
+      <c r="Q24">
+        <v>11.58756584</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.07561718468684463</v>
+      </c>
+      <c r="T24">
+        <v>0.8003735801487962</v>
+      </c>
+      <c r="U24">
+        <v>0.0495</v>
+      </c>
+      <c r="V24">
+        <v>0.28</v>
+      </c>
+      <c r="W24">
+        <v>0.03564</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>6.995313140196068</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.06670491700186405</v>
+      </c>
+      <c r="C25">
+        <v>62.1334479999792</v>
+      </c>
+      <c r="D25">
+        <v>76.8544479999792</v>
+      </c>
+      <c r="E25">
+        <v>-9.478999999999999</v>
+      </c>
+      <c r="F25">
+        <v>19.021</v>
+      </c>
+      <c r="G25">
+        <v>4.3</v>
+      </c>
+      <c r="H25">
+        <v>54.2</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>14</v>
+      </c>
+      <c r="K25">
+        <v>7.7</v>
+      </c>
+      <c r="L25">
+        <v>6.3</v>
+      </c>
+      <c r="M25">
+        <v>0.9415395000000001</v>
+      </c>
+      <c r="N25">
+        <v>5.3584605</v>
+      </c>
+      <c r="O25">
+        <v>1.50036894</v>
+      </c>
+      <c r="P25">
+        <v>3.85809156</v>
+      </c>
+      <c r="Q25">
+        <v>11.55809156</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.0759840480543689</v>
+      </c>
+      <c r="T25">
+        <v>0.8083488707471499</v>
+      </c>
+      <c r="U25">
+        <v>0.0495</v>
+      </c>
+      <c r="V25">
+        <v>0.28</v>
+      </c>
+      <c r="W25">
+        <v>0.03564</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>6.691169090622326</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.06658762994798929</v>
+      </c>
+      <c r="C26">
+        <v>61.37904016829972</v>
+      </c>
+      <c r="D26">
+        <v>76.92704016829973</v>
+      </c>
+      <c r="E26">
+        <v>-8.652000000000001</v>
+      </c>
+      <c r="F26">
+        <v>19.848</v>
+      </c>
+      <c r="G26">
+        <v>4.3</v>
+      </c>
+      <c r="H26">
+        <v>54.2</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>14</v>
+      </c>
+      <c r="K26">
+        <v>7.7</v>
+      </c>
+      <c r="L26">
+        <v>6.3</v>
+      </c>
+      <c r="M26">
+        <v>0.982476</v>
+      </c>
+      <c r="N26">
+        <v>5.317524</v>
+      </c>
+      <c r="O26">
+        <v>1.48890672</v>
+      </c>
+      <c r="P26">
+        <v>3.82861728</v>
+      </c>
+      <c r="Q26">
+        <v>11.52861728</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.07636056572103855</v>
+      </c>
+      <c r="T26">
+        <v>0.8165340374138815</v>
+      </c>
+      <c r="U26">
+        <v>0.0495</v>
+      </c>
+      <c r="V26">
+        <v>0.28</v>
+      </c>
+      <c r="W26">
+        <v>0.03564</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>6.412370378513063</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.06672234289411455</v>
+      </c>
+      <c r="C27">
+        <v>60.46867432633755</v>
+      </c>
+      <c r="D27">
+        <v>76.84367432633755</v>
+      </c>
+      <c r="E27">
+        <v>-7.824999999999999</v>
+      </c>
+      <c r="F27">
+        <v>20.675</v>
+      </c>
+      <c r="G27">
+        <v>4.3</v>
+      </c>
+      <c r="H27">
+        <v>54.2</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>14</v>
+      </c>
+      <c r="K27">
+        <v>7.7</v>
+      </c>
+      <c r="L27">
+        <v>6.3</v>
+      </c>
+      <c r="M27">
+        <v>1.0523575</v>
+      </c>
+      <c r="N27">
+        <v>5.2476425</v>
+      </c>
+      <c r="O27">
+        <v>1.4693399</v>
+      </c>
+      <c r="P27">
+        <v>3.7783026</v>
+      </c>
+      <c r="Q27">
+        <v>11.4783026</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.07674712385881939</v>
+      </c>
+      <c r="T27">
+        <v>0.8249374751917259</v>
+      </c>
+      <c r="U27">
+        <v>0.0509</v>
+      </c>
+      <c r="V27">
+        <v>0.28</v>
+      </c>
+      <c r="W27">
+        <v>0.036648</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>5.986558750234591</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.0666151358402398</v>
+      </c>
+      <c r="C28">
+        <v>59.70800371239188</v>
+      </c>
+      <c r="D28">
+        <v>76.91000371239188</v>
+      </c>
+      <c r="E28">
+        <v>-6.997999999999998</v>
+      </c>
+      <c r="F28">
+        <v>21.502</v>
+      </c>
+      <c r="G28">
+        <v>4.3</v>
+      </c>
+      <c r="H28">
+        <v>54.2</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>14</v>
+      </c>
+      <c r="K28">
+        <v>7.7</v>
+      </c>
+      <c r="L28">
+        <v>6.3</v>
+      </c>
+      <c r="M28">
+        <v>1.0944518</v>
+      </c>
+      <c r="N28">
+        <v>5.2055482</v>
+      </c>
+      <c r="O28">
+        <v>1.457553496</v>
+      </c>
+      <c r="P28">
+        <v>3.747994704</v>
+      </c>
+      <c r="Q28">
+        <v>11.447994704</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.07714412951383756</v>
+      </c>
+      <c r="T28">
+        <v>0.8335680329095121</v>
+      </c>
+      <c r="U28">
+        <v>0.0509</v>
+      </c>
+      <c r="V28">
+        <v>0.28</v>
+      </c>
+      <c r="W28">
+        <v>0.036648</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>5.756306490610185</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.06650792878636504</v>
+      </c>
+      <c r="C29">
+        <v>58.94744770484368</v>
+      </c>
+      <c r="D29">
+        <v>76.97644770484368</v>
+      </c>
+      <c r="E29">
+        <v>-6.170999999999999</v>
+      </c>
+      <c r="F29">
+        <v>22.329</v>
+      </c>
+      <c r="G29">
+        <v>4.3</v>
+      </c>
+      <c r="H29">
+        <v>54.2</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>14</v>
+      </c>
+      <c r="K29">
+        <v>7.7</v>
+      </c>
+      <c r="L29">
+        <v>6.3</v>
+      </c>
+      <c r="M29">
+        <v>1.1365461</v>
+      </c>
+      <c r="N29">
+        <v>5.163453899999999</v>
+      </c>
+      <c r="O29">
+        <v>1.445767092</v>
+      </c>
+      <c r="P29">
+        <v>3.717686807999999</v>
+      </c>
+      <c r="Q29">
+        <v>11.417686808</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.07755201203611649</v>
+      </c>
+      <c r="T29">
+        <v>0.8424350442634019</v>
+      </c>
+      <c r="U29">
+        <v>0.0509</v>
+      </c>
+      <c r="V29">
+        <v>0.28</v>
+      </c>
+      <c r="W29">
+        <v>0.036648</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>5.543109953920918</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.06640072173249029</v>
+      </c>
+      <c r="C30">
+        <v>58.18700660098158</v>
+      </c>
+      <c r="D30">
+        <v>77.04300660098158</v>
+      </c>
+      <c r="E30">
+        <v>-5.343999999999998</v>
+      </c>
+      <c r="F30">
+        <v>23.156</v>
+      </c>
+      <c r="G30">
+        <v>4.3</v>
+      </c>
+      <c r="H30">
+        <v>54.2</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>14</v>
+      </c>
+      <c r="K30">
+        <v>7.7</v>
+      </c>
+      <c r="L30">
+        <v>6.3</v>
+      </c>
+      <c r="M30">
+        <v>1.1786404</v>
+      </c>
+      <c r="N30">
+        <v>5.1213596</v>
+      </c>
+      <c r="O30">
+        <v>1.433980688</v>
+      </c>
+      <c r="P30">
+        <v>3.687378912</v>
+      </c>
+      <c r="Q30">
+        <v>11.387378912</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.07797122462845874</v>
+      </c>
+      <c r="T30">
+        <v>0.8515483614882332</v>
+      </c>
+      <c r="U30">
+        <v>0.0509</v>
+      </c>
+      <c r="V30">
+        <v>0.28</v>
+      </c>
+      <c r="W30">
+        <v>0.036648</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>5.345141741280885</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.06629351467861552</v>
+      </c>
+      <c r="C31">
+        <v>57.42668069912337</v>
+      </c>
+      <c r="D31">
+        <v>77.10968069912337</v>
+      </c>
+      <c r="E31">
+        <v>-4.516999999999999</v>
+      </c>
+      <c r="F31">
+        <v>23.983</v>
+      </c>
+      <c r="G31">
+        <v>4.3</v>
+      </c>
+      <c r="H31">
+        <v>54.2</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>14</v>
+      </c>
+      <c r="K31">
+        <v>7.7</v>
+      </c>
+      <c r="L31">
+        <v>6.3</v>
+      </c>
+      <c r="M31">
+        <v>1.2207347</v>
+      </c>
+      <c r="N31">
+        <v>5.079265299999999</v>
+      </c>
+      <c r="O31">
+        <v>1.422194284</v>
+      </c>
+      <c r="P31">
+        <v>3.657071016</v>
+      </c>
+      <c r="Q31">
+        <v>11.357071016</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.07840224602621906</v>
+      </c>
+      <c r="T31">
+        <v>0.8609183918743273</v>
+      </c>
+      <c r="U31">
+        <v>0.0509</v>
+      </c>
+      <c r="V31">
+        <v>0.28</v>
+      </c>
+      <c r="W31">
+        <v>0.036648</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>5.160826508822924</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.06618630762474077</v>
+      </c>
+      <c r="C32">
+        <v>56.66647029862041</v>
+      </c>
+      <c r="D32">
+        <v>77.17647029862042</v>
+      </c>
+      <c r="E32">
+        <v>-3.690000000000001</v>
+      </c>
+      <c r="F32">
+        <v>24.81</v>
+      </c>
+      <c r="G32">
+        <v>4.3</v>
+      </c>
+      <c r="H32">
+        <v>54.2</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>14</v>
+      </c>
+      <c r="K32">
+        <v>7.7</v>
+      </c>
+      <c r="L32">
+        <v>6.3</v>
+      </c>
+      <c r="M32">
+        <v>1.262829</v>
+      </c>
+      <c r="N32">
+        <v>5.037171</v>
+      </c>
+      <c r="O32">
+        <v>1.41040788</v>
+      </c>
+      <c r="P32">
+        <v>3.62676312</v>
+      </c>
+      <c r="Q32">
+        <v>11.32676312</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.07884558232105826</v>
+      </c>
+      <c r="T32">
+        <v>0.8705561374143099</v>
+      </c>
+      <c r="U32">
+        <v>0.0509</v>
+      </c>
+      <c r="V32">
+        <v>0.28</v>
+      </c>
+      <c r="W32">
+        <v>0.036648</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>4.988798958528827</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.06607910057086601</v>
+      </c>
+      <c r="C33">
+        <v>55.9063756998621</v>
+      </c>
+      <c r="D33">
+        <v>77.2433756998621</v>
+      </c>
+      <c r="E33">
+        <v>-2.863</v>
+      </c>
+      <c r="F33">
+        <v>25.637</v>
+      </c>
+      <c r="G33">
+        <v>4.3</v>
+      </c>
+      <c r="H33">
+        <v>54.2</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>14</v>
+      </c>
+      <c r="K33">
+        <v>7.7</v>
+      </c>
+      <c r="L33">
+        <v>6.3</v>
+      </c>
+      <c r="M33">
+        <v>1.3049233</v>
+      </c>
+      <c r="N33">
+        <v>4.9950767</v>
+      </c>
+      <c r="O33">
+        <v>1.398621476</v>
+      </c>
+      <c r="P33">
+        <v>3.596455224</v>
+      </c>
+      <c r="Q33">
+        <v>11.296455224</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.07930176894328408</v>
+      </c>
+      <c r="T33">
+        <v>0.8804732378974802</v>
+      </c>
+      <c r="U33">
+        <v>0.0509</v>
+      </c>
+      <c r="V33">
+        <v>0.28</v>
+      </c>
+      <c r="W33">
+        <v>0.036648</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>4.827869959866607</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.06597189351699126</v>
+      </c>
+      <c r="C34">
+        <v>55.14639720428039</v>
+      </c>
+      <c r="D34">
+        <v>77.31039720428039</v>
+      </c>
+      <c r="E34">
+        <v>-2.035999999999998</v>
+      </c>
+      <c r="F34">
+        <v>26.464</v>
+      </c>
+      <c r="G34">
+        <v>4.3</v>
+      </c>
+      <c r="H34">
+        <v>54.2</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>14</v>
+      </c>
+      <c r="K34">
+        <v>7.7</v>
+      </c>
+      <c r="L34">
+        <v>6.3</v>
+      </c>
+      <c r="M34">
+        <v>1.3470176</v>
+      </c>
+      <c r="N34">
+        <v>4.9529824</v>
+      </c>
+      <c r="O34">
+        <v>1.386835072</v>
+      </c>
+      <c r="P34">
+        <v>3.566147328</v>
+      </c>
+      <c r="Q34">
+        <v>11.266147328</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.0797713728191048</v>
+      </c>
+      <c r="T34">
+        <v>0.8906820178066263</v>
+      </c>
+      <c r="U34">
+        <v>0.0509</v>
+      </c>
+      <c r="V34">
+        <v>0.28</v>
+      </c>
+      <c r="W34">
+        <v>0.036648</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>4.676999023620775</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.06586468646311651</v>
+      </c>
+      <c r="C35">
+        <v>54.3865351143543</v>
+      </c>
+      <c r="D35">
+        <v>77.3775351143543</v>
+      </c>
+      <c r="E35">
+        <v>-1.208999999999996</v>
+      </c>
+      <c r="F35">
+        <v>27.291</v>
+      </c>
+      <c r="G35">
+        <v>4.3</v>
+      </c>
+      <c r="H35">
+        <v>54.2</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>14</v>
+      </c>
+      <c r="K35">
+        <v>7.7</v>
+      </c>
+      <c r="L35">
+        <v>6.3</v>
+      </c>
+      <c r="M35">
+        <v>1.3891119</v>
+      </c>
+      <c r="N35">
+        <v>4.910888099999999</v>
+      </c>
+      <c r="O35">
+        <v>1.375048668</v>
+      </c>
+      <c r="P35">
+        <v>3.535839432</v>
+      </c>
+      <c r="Q35">
+        <v>11.235839432</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.08025499472106942</v>
+      </c>
+      <c r="T35">
+        <v>0.9011955374145528</v>
+      </c>
+      <c r="U35">
+        <v>0.0509</v>
+      </c>
+      <c r="V35">
+        <v>0.28</v>
+      </c>
+      <c r="W35">
+        <v>0.036648</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>4.53527178048075</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.06639395940924177</v>
+      </c>
+      <c r="C36">
+        <v>53.22920881067959</v>
+      </c>
+      <c r="D36">
+        <v>77.04720881067959</v>
+      </c>
+      <c r="E36">
+        <v>-0.3819999999999979</v>
+      </c>
+      <c r="F36">
+        <v>28.118</v>
+      </c>
+      <c r="G36">
+        <v>4.3</v>
+      </c>
+      <c r="H36">
+        <v>54.2</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>14</v>
+      </c>
+      <c r="K36">
+        <v>7.7</v>
+      </c>
+      <c r="L36">
+        <v>6.3</v>
+      </c>
+      <c r="M36">
+        <v>1.504313</v>
+      </c>
+      <c r="N36">
+        <v>4.795687</v>
+      </c>
+      <c r="O36">
+        <v>1.34279236</v>
+      </c>
+      <c r="P36">
+        <v>3.45289464</v>
+      </c>
+      <c r="Q36">
+        <v>11.15289464</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.0807532718321845</v>
+      </c>
+      <c r="T36">
+        <v>0.9120276485257499</v>
+      </c>
+      <c r="U36">
+        <v>0.0535</v>
+      </c>
+      <c r="V36">
+        <v>0.28</v>
+      </c>
+      <c r="W36">
+        <v>0.03852</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>4.187958224119582</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.06630547235536702</v>
+      </c>
+      <c r="C37">
+        <v>52.45723827594301</v>
+      </c>
+      <c r="D37">
+        <v>77.10223827594302</v>
+      </c>
+      <c r="E37">
+        <v>0.4450000000000038</v>
+      </c>
+      <c r="F37">
+        <v>28.945</v>
+      </c>
+      <c r="G37">
+        <v>4.3</v>
+      </c>
+      <c r="H37">
+        <v>54.2</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>14</v>
+      </c>
+      <c r="K37">
+        <v>7.7</v>
+      </c>
+      <c r="L37">
+        <v>6.3</v>
+      </c>
+      <c r="M37">
+        <v>1.5485575</v>
+      </c>
+      <c r="N37">
+        <v>4.7514425</v>
+      </c>
+      <c r="O37">
+        <v>1.3304039</v>
+      </c>
+      <c r="P37">
+        <v>3.421038599999999</v>
+      </c>
+      <c r="Q37">
+        <v>11.1210386</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.08126688054671849</v>
+      </c>
+      <c r="T37">
+        <v>0.9231930553634452</v>
+      </c>
+      <c r="U37">
+        <v>0.0535</v>
+      </c>
+      <c r="V37">
+        <v>0.28</v>
+      </c>
+      <c r="W37">
+        <v>0.03852</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>4.068302274859022</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.06691682530149226</v>
+      </c>
+      <c r="C38">
+        <v>51.25163893897103</v>
+      </c>
+      <c r="D38">
+        <v>76.72363893897104</v>
+      </c>
+      <c r="E38">
+        <v>1.271999999999998</v>
+      </c>
+      <c r="F38">
+        <v>29.772</v>
+      </c>
+      <c r="G38">
+        <v>4.3</v>
+      </c>
+      <c r="H38">
+        <v>54.2</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>14</v>
+      </c>
+      <c r="K38">
+        <v>7.7</v>
+      </c>
+      <c r="L38">
+        <v>6.3</v>
+      </c>
+      <c r="M38">
+        <v>1.6731864</v>
+      </c>
+      <c r="N38">
+        <v>4.6268136</v>
+      </c>
+      <c r="O38">
+        <v>1.295507808</v>
+      </c>
+      <c r="P38">
+        <v>3.331305792</v>
+      </c>
+      <c r="Q38">
+        <v>11.031305792</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.08179653953358165</v>
+      </c>
+      <c r="T38">
+        <v>0.9347073811648186</v>
+      </c>
+      <c r="U38">
+        <v>0.0562</v>
+      </c>
+      <c r="V38">
+        <v>0.28</v>
+      </c>
+      <c r="W38">
+        <v>0.040464</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>3.765270862827955</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.06684777824761751</v>
+      </c>
+      <c r="C39">
+        <v>50.46721212164412</v>
+      </c>
+      <c r="D39">
+        <v>76.76621212164413</v>
+      </c>
+      <c r="E39">
+        <v>2.099</v>
+      </c>
+      <c r="F39">
+        <v>30.599</v>
+      </c>
+      <c r="G39">
+        <v>4.3</v>
+      </c>
+      <c r="H39">
+        <v>54.2</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>14</v>
+      </c>
+      <c r="K39">
+        <v>7.7</v>
+      </c>
+      <c r="L39">
+        <v>6.3</v>
+      </c>
+      <c r="M39">
+        <v>1.7196638</v>
+      </c>
+      <c r="N39">
+        <v>4.5803362</v>
+      </c>
+      <c r="O39">
+        <v>1.282494136</v>
+      </c>
+      <c r="P39">
+        <v>3.297842064</v>
+      </c>
+      <c r="Q39">
+        <v>10.997842064</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.08234301309145636</v>
+      </c>
+      <c r="T39">
+        <v>0.9465872411186164</v>
+      </c>
+      <c r="U39">
+        <v>0.0562</v>
+      </c>
+      <c r="V39">
+        <v>0.28</v>
+      </c>
+      <c r="W39">
+        <v>0.040464</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>3.663506785454226</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.06677873119374275</v>
+      </c>
+      <c r="C40">
+        <v>49.6828325774182</v>
+      </c>
+      <c r="D40">
+        <v>76.8088325774182</v>
+      </c>
+      <c r="E40">
+        <v>2.926000000000002</v>
+      </c>
+      <c r="F40">
+        <v>31.426</v>
+      </c>
+      <c r="G40">
+        <v>4.3</v>
+      </c>
+      <c r="H40">
+        <v>54.2</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>14</v>
+      </c>
+      <c r="K40">
+        <v>7.7</v>
+      </c>
+      <c r="L40">
+        <v>6.3</v>
+      </c>
+      <c r="M40">
+        <v>1.7661412</v>
+      </c>
+      <c r="N40">
+        <v>4.5338588</v>
+      </c>
+      <c r="O40">
+        <v>1.269480464</v>
+      </c>
+      <c r="P40">
+        <v>3.264378336</v>
+      </c>
+      <c r="Q40">
+        <v>10.964378336</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.08290711482861735</v>
+      </c>
+      <c r="T40">
+        <v>0.9588503223612466</v>
+      </c>
+      <c r="U40">
+        <v>0.0562</v>
+      </c>
+      <c r="V40">
+        <v>0.28</v>
+      </c>
+      <c r="W40">
+        <v>0.040464</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>3.5670987121528</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.06802944413986799</v>
+      </c>
+      <c r="C41">
+        <v>48.09107140298147</v>
+      </c>
+      <c r="D41">
+        <v>76.04407140298147</v>
+      </c>
+      <c r="E41">
+        <v>3.753</v>
+      </c>
+      <c r="F41">
+        <v>32.253</v>
+      </c>
+      <c r="G41">
+        <v>4.3</v>
+      </c>
+      <c r="H41">
+        <v>54.2</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>14</v>
+      </c>
+      <c r="K41">
+        <v>7.7</v>
+      </c>
+      <c r="L41">
+        <v>6.3</v>
+      </c>
+      <c r="M41">
+        <v>1.9642077</v>
+      </c>
+      <c r="N41">
+        <v>4.3357923</v>
+      </c>
+      <c r="O41">
+        <v>1.214021844</v>
+      </c>
+      <c r="P41">
+        <v>3.121770456</v>
+      </c>
+      <c r="Q41">
+        <v>10.821770456</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.08348971170470162</v>
+      </c>
+      <c r="T41">
+        <v>0.9715154718413398</v>
+      </c>
+      <c r="U41">
+        <v>0.0609</v>
+      </c>
+      <c r="V41">
+        <v>0.28</v>
+      </c>
+      <c r="W41">
+        <v>0.043848</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>3.207400113541964</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.06799423708599325</v>
+      </c>
+      <c r="C42">
+        <v>47.28539074551345</v>
+      </c>
+      <c r="D42">
+        <v>76.06539074551345</v>
+      </c>
+      <c r="E42">
+        <v>4.580000000000005</v>
+      </c>
+      <c r="F42">
+        <v>33.08000000000001</v>
+      </c>
+      <c r="G42">
+        <v>4.3</v>
+      </c>
+      <c r="H42">
+        <v>54.2</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>14</v>
+      </c>
+      <c r="K42">
+        <v>7.7</v>
+      </c>
+      <c r="L42">
+        <v>6.3</v>
+      </c>
+      <c r="M42">
+        <v>2.014572</v>
+      </c>
+      <c r="N42">
+        <v>4.285428</v>
+      </c>
+      <c r="O42">
+        <v>1.19991984</v>
+      </c>
+      <c r="P42">
+        <v>3.08550816</v>
+      </c>
+      <c r="Q42">
+        <v>10.78550816</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.08409172847665541</v>
+      </c>
+      <c r="T42">
+        <v>0.9846027929707697</v>
+      </c>
+      <c r="U42">
+        <v>0.0609</v>
+      </c>
+      <c r="V42">
+        <v>0.28</v>
+      </c>
+      <c r="W42">
+        <v>0.043848</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>3.127215110703415</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.06795903003211849</v>
+      </c>
+      <c r="C43">
+        <v>46.47972204537016</v>
+      </c>
+      <c r="D43">
+        <v>76.08672204537017</v>
+      </c>
+      <c r="E43">
+        <v>5.407000000000004</v>
+      </c>
+      <c r="F43">
+        <v>33.907</v>
+      </c>
+      <c r="G43">
+        <v>4.3</v>
+      </c>
+      <c r="H43">
+        <v>54.2</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>14</v>
+      </c>
+      <c r="K43">
+        <v>7.7</v>
+      </c>
+      <c r="L43">
+        <v>6.3</v>
+      </c>
+      <c r="M43">
+        <v>2.0649363</v>
+      </c>
+      <c r="N43">
+        <v>4.2350637</v>
+      </c>
+      <c r="O43">
+        <v>1.185817836</v>
+      </c>
+      <c r="P43">
+        <v>3.049245864</v>
+      </c>
+      <c r="Q43">
+        <v>10.749245864</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.084714152596811</v>
+      </c>
+      <c r="T43">
+        <v>0.998133752104587</v>
+      </c>
+      <c r="U43">
+        <v>0.0609</v>
+      </c>
+      <c r="V43">
+        <v>0.28</v>
+      </c>
+      <c r="W43">
+        <v>0.043848</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>3.050941571417965</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.07073614297824374</v>
+      </c>
+      <c r="C44">
+        <v>44.006073660554</v>
+      </c>
+      <c r="D44">
+        <v>74.44007366055401</v>
+      </c>
+      <c r="E44">
+        <v>6.234000000000002</v>
+      </c>
+      <c r="F44">
+        <v>34.734</v>
+      </c>
+      <c r="G44">
+        <v>4.3</v>
+      </c>
+      <c r="H44">
+        <v>54.2</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>14</v>
+      </c>
+      <c r="K44">
+        <v>7.7</v>
+      </c>
+      <c r="L44">
+        <v>6.3</v>
+      </c>
+      <c r="M44">
+        <v>2.4383268</v>
+      </c>
+      <c r="N44">
+        <v>3.8616732</v>
+      </c>
+      <c r="O44">
+        <v>1.081268496</v>
+      </c>
+      <c r="P44">
+        <v>2.780404704</v>
+      </c>
+      <c r="Q44">
+        <v>10.480404704</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.08535803961766161</v>
+      </c>
+      <c r="T44">
+        <v>1.012131296036122</v>
+      </c>
+      <c r="U44">
+        <v>0.0702</v>
+      </c>
+      <c r="V44">
+        <v>0.28</v>
+      </c>
+      <c r="W44">
+        <v>0.050544</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>2.583738980353249</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.07076789592436898</v>
+      </c>
+      <c r="C45">
+        <v>43.16065823224231</v>
+      </c>
+      <c r="D45">
+        <v>74.42165823224231</v>
+      </c>
+      <c r="E45">
+        <v>7.061</v>
+      </c>
+      <c r="F45">
+        <v>35.561</v>
+      </c>
+      <c r="G45">
+        <v>4.3</v>
+      </c>
+      <c r="H45">
+        <v>54.2</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>14</v>
+      </c>
+      <c r="K45">
+        <v>7.7</v>
+      </c>
+      <c r="L45">
+        <v>6.3</v>
+      </c>
+      <c r="M45">
+        <v>2.4963822</v>
+      </c>
+      <c r="N45">
+        <v>3.8036178</v>
+      </c>
+      <c r="O45">
+        <v>1.065012984</v>
+      </c>
+      <c r="P45">
+        <v>2.738604816</v>
+      </c>
+      <c r="Q45">
+        <v>10.438604816</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.08602451916555962</v>
+      </c>
+      <c r="T45">
+        <v>1.026619981859992</v>
+      </c>
+      <c r="U45">
+        <v>0.0702</v>
+      </c>
+      <c r="V45">
+        <v>0.28</v>
+      </c>
+      <c r="W45">
+        <v>0.050544</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>2.523652027321778</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.07228860887049424</v>
+      </c>
+      <c r="C46">
+        <v>41.46224852951269</v>
+      </c>
+      <c r="D46">
+        <v>73.55024852951269</v>
+      </c>
+      <c r="E46">
+        <v>7.887999999999998</v>
+      </c>
+      <c r="F46">
+        <v>36.388</v>
+      </c>
+      <c r="G46">
+        <v>4.3</v>
+      </c>
+      <c r="H46">
+        <v>54.2</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>14</v>
+      </c>
+      <c r="K46">
+        <v>7.7</v>
+      </c>
+      <c r="L46">
+        <v>6.3</v>
+      </c>
+      <c r="M46">
+        <v>2.7254612</v>
+      </c>
+      <c r="N46">
+        <v>3.5745388</v>
+      </c>
+      <c r="O46">
+        <v>1.000870864</v>
+      </c>
+      <c r="P46">
+        <v>2.573667936</v>
+      </c>
+      <c r="Q46">
+        <v>10.273667936</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.08671480155445399</v>
+      </c>
+      <c r="T46">
+        <v>1.041626120749</v>
+      </c>
+      <c r="U46">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V46">
+        <v>0.28</v>
+      </c>
+      <c r="W46">
+        <v>0.053928</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>2.311535383442626</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.07235420181661947</v>
+      </c>
+      <c r="C47">
+        <v>40.5981208502583</v>
+      </c>
+      <c r="D47">
+        <v>73.5131208502583</v>
+      </c>
+      <c r="E47">
+        <v>8.715000000000003</v>
+      </c>
+      <c r="F47">
+        <v>37.215</v>
+      </c>
+      <c r="G47">
+        <v>4.3</v>
+      </c>
+      <c r="H47">
+        <v>54.2</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>14</v>
+      </c>
+      <c r="K47">
+        <v>7.7</v>
+      </c>
+      <c r="L47">
+        <v>6.3</v>
+      </c>
+      <c r="M47">
+        <v>2.7874035</v>
+      </c>
+      <c r="N47">
+        <v>3.5125965</v>
+      </c>
+      <c r="O47">
+        <v>0.98352702</v>
+      </c>
+      <c r="P47">
+        <v>2.52906948</v>
+      </c>
+      <c r="Q47">
+        <v>10.22906948</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.08743018512112632</v>
+      </c>
+      <c r="T47">
+        <v>1.057177937415789</v>
+      </c>
+      <c r="U47">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V47">
+        <v>0.28</v>
+      </c>
+      <c r="W47">
+        <v>0.053928</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>2.260167930477234</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.07241979476274472</v>
+      </c>
+      <c r="C48">
+        <v>39.73403063570608</v>
+      </c>
+      <c r="D48">
+        <v>73.47603063570608</v>
+      </c>
+      <c r="E48">
+        <v>9.542000000000002</v>
+      </c>
+      <c r="F48">
+        <v>38.042</v>
+      </c>
+      <c r="G48">
+        <v>4.3</v>
+      </c>
+      <c r="H48">
+        <v>54.2</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>14</v>
+      </c>
+      <c r="K48">
+        <v>7.7</v>
+      </c>
+      <c r="L48">
+        <v>6.3</v>
+      </c>
+      <c r="M48">
+        <v>2.8493458</v>
+      </c>
+      <c r="N48">
+        <v>3.4506542</v>
+      </c>
+      <c r="O48">
+        <v>0.966183176</v>
+      </c>
+      <c r="P48">
+        <v>2.484471024</v>
+      </c>
+      <c r="Q48">
+        <v>10.184471024</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.08817206437545319</v>
+      </c>
+      <c r="T48">
+        <v>1.073305747292461</v>
+      </c>
+      <c r="U48">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V48">
+        <v>0.28</v>
+      </c>
+      <c r="W48">
+        <v>0.053928</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>2.211033845032077</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.07248538770886997</v>
+      </c>
+      <c r="C49">
+        <v>38.86997782917746</v>
+      </c>
+      <c r="D49">
+        <v>73.43897782917747</v>
+      </c>
+      <c r="E49">
+        <v>10.36900000000001</v>
+      </c>
+      <c r="F49">
+        <v>38.86900000000001</v>
+      </c>
+      <c r="G49">
+        <v>4.3</v>
+      </c>
+      <c r="H49">
+        <v>54.2</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>14</v>
+      </c>
+      <c r="K49">
+        <v>7.7</v>
+      </c>
+      <c r="L49">
+        <v>6.3</v>
+      </c>
+      <c r="M49">
+        <v>2.9112881</v>
+      </c>
+      <c r="N49">
+        <v>3.3887119</v>
+      </c>
+      <c r="O49">
+        <v>0.948839332</v>
+      </c>
+      <c r="P49">
+        <v>2.439872568</v>
+      </c>
+      <c r="Q49">
+        <v>10.139872568</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.08894193907333957</v>
+      </c>
+      <c r="T49">
+        <v>1.090042153768251</v>
+      </c>
+      <c r="U49">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V49">
+        <v>0.28</v>
+      </c>
+      <c r="W49">
+        <v>0.053928</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>2.163990571733522</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.07255098065499521</v>
+      </c>
+      <c r="C50">
+        <v>38.00596237410815</v>
+      </c>
+      <c r="D50">
+        <v>73.40196237410815</v>
+      </c>
+      <c r="E50">
+        <v>11.196</v>
+      </c>
+      <c r="F50">
+        <v>39.696</v>
+      </c>
+      <c r="G50">
+        <v>4.3</v>
+      </c>
+      <c r="H50">
+        <v>54.2</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>14</v>
+      </c>
+      <c r="K50">
+        <v>7.7</v>
+      </c>
+      <c r="L50">
+        <v>6.3</v>
+      </c>
+      <c r="M50">
+        <v>2.9732304</v>
+      </c>
+      <c r="N50">
+        <v>3.3267696</v>
+      </c>
+      <c r="O50">
+        <v>0.931495488</v>
+      </c>
+      <c r="P50">
+        <v>2.395274112</v>
+      </c>
+      <c r="Q50">
+        <v>10.095274112</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.08974142433652925</v>
+      </c>
+      <c r="T50">
+        <v>1.107422268185418</v>
+      </c>
+      <c r="U50">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V50">
+        <v>0.28</v>
+      </c>
+      <c r="W50">
+        <v>0.053928</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>2.118907434822408</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.07261657360112045</v>
+      </c>
+      <c r="C51">
+        <v>37.14198421404779</v>
+      </c>
+      <c r="D51">
+        <v>73.36498421404779</v>
+      </c>
+      <c r="E51">
+        <v>12.023</v>
+      </c>
+      <c r="F51">
+        <v>40.523</v>
+      </c>
+      <c r="G51">
+        <v>4.3</v>
+      </c>
+      <c r="H51">
+        <v>54.2</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>14</v>
+      </c>
+      <c r="K51">
+        <v>7.7</v>
+      </c>
+      <c r="L51">
+        <v>6.3</v>
+      </c>
+      <c r="M51">
+        <v>3.0351727</v>
+      </c>
+      <c r="N51">
+        <v>3.2648273</v>
+      </c>
+      <c r="O51">
+        <v>0.914151644</v>
+      </c>
+      <c r="P51">
+        <v>2.350675656</v>
+      </c>
+      <c r="Q51">
+        <v>10.050675656</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.09057226196298129</v>
+      </c>
+      <c r="T51">
+        <v>1.125483955716985</v>
+      </c>
+      <c r="U51">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V51">
+        <v>0.28</v>
+      </c>
+      <c r="W51">
+        <v>0.053928</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>2.075664425948481</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.07268216654724571</v>
+      </c>
+      <c r="C52">
+        <v>36.27804329265975</v>
+      </c>
+      <c r="D52">
+        <v>73.32804329265976</v>
+      </c>
+      <c r="E52">
+        <v>12.85</v>
+      </c>
+      <c r="F52">
+        <v>41.35</v>
+      </c>
+      <c r="G52">
+        <v>4.3</v>
+      </c>
+      <c r="H52">
+        <v>54.2</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>14</v>
+      </c>
+      <c r="K52">
+        <v>7.7</v>
+      </c>
+      <c r="L52">
+        <v>6.3</v>
+      </c>
+      <c r="M52">
+        <v>3.097115</v>
+      </c>
+      <c r="N52">
+        <v>3.202885</v>
+      </c>
+      <c r="O52">
+        <v>0.8968078</v>
+      </c>
+      <c r="P52">
+        <v>2.3060772</v>
+      </c>
+      <c r="Q52">
+        <v>10.0060772</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.09143633309449142</v>
+      </c>
+      <c r="T52">
+        <v>1.144268110749813</v>
+      </c>
+      <c r="U52">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V52">
+        <v>0.28</v>
+      </c>
+      <c r="W52">
+        <v>0.053928</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>2.034151137429511</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.07873311949337096</v>
+      </c>
+      <c r="C53">
+        <v>32.19614700314526</v>
+      </c>
+      <c r="D53">
+        <v>70.07314700314527</v>
+      </c>
+      <c r="E53">
+        <v>13.677</v>
+      </c>
+      <c r="F53">
+        <v>42.177</v>
+      </c>
+      <c r="G53">
+        <v>4.3</v>
+      </c>
+      <c r="H53">
+        <v>54.2</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>14</v>
+      </c>
+      <c r="K53">
+        <v>7.7</v>
+      </c>
+      <c r="L53">
+        <v>6.3</v>
+      </c>
+      <c r="M53">
+        <v>3.8465424</v>
+      </c>
+      <c r="N53">
+        <v>2.4534576</v>
+      </c>
+      <c r="O53">
+        <v>0.686968128</v>
+      </c>
+      <c r="P53">
+        <v>1.766489472</v>
+      </c>
+      <c r="Q53">
+        <v>9.466489471999999</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.09233567243545093</v>
+      </c>
+      <c r="T53">
+        <v>1.163818965988064</v>
+      </c>
+      <c r="U53">
+        <v>0.0912</v>
+      </c>
+      <c r="V53">
+        <v>0.28</v>
+      </c>
+      <c r="W53">
+        <v>0.065664</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>1.637834539403491</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.07891607243949619</v>
+      </c>
+      <c r="C54">
+        <v>31.27522835346093</v>
+      </c>
+      <c r="D54">
+        <v>69.97922835346094</v>
+      </c>
+      <c r="E54">
+        <v>14.504</v>
+      </c>
+      <c r="F54">
+        <v>43.004</v>
+      </c>
+      <c r="G54">
+        <v>4.3</v>
+      </c>
+      <c r="H54">
+        <v>54.2</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>14</v>
+      </c>
+      <c r="K54">
+        <v>7.7</v>
+      </c>
+      <c r="L54">
+        <v>6.3</v>
+      </c>
+      <c r="M54">
+        <v>3.9219648</v>
+      </c>
+      <c r="N54">
+        <v>2.378035199999999</v>
+      </c>
+      <c r="O54">
+        <v>0.6658498559999999</v>
+      </c>
+      <c r="P54">
+        <v>1.712185343999999</v>
+      </c>
+      <c r="Q54">
+        <v>9.412185343999999</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.09327248424895042</v>
+      </c>
+      <c r="T54">
+        <v>1.184184440194574</v>
+      </c>
+      <c r="U54">
+        <v>0.0912</v>
+      </c>
+      <c r="V54">
+        <v>0.28</v>
+      </c>
+      <c r="W54">
+        <v>0.065664</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>1.606337721338039</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.07909902538562144</v>
+      </c>
+      <c r="C55">
+        <v>30.35456112408831</v>
+      </c>
+      <c r="D55">
+        <v>69.88556112408831</v>
+      </c>
+      <c r="E55">
+        <v>15.331</v>
+      </c>
+      <c r="F55">
+        <v>43.831</v>
+      </c>
+      <c r="G55">
+        <v>4.3</v>
+      </c>
+      <c r="H55">
+        <v>54.2</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>14</v>
+      </c>
+      <c r="K55">
+        <v>7.7</v>
+      </c>
+      <c r="L55">
+        <v>6.3</v>
+      </c>
+      <c r="M55">
+        <v>3.9973872</v>
+      </c>
+      <c r="N55">
+        <v>2.302612799999999</v>
+      </c>
+      <c r="O55">
+        <v>0.6447315839999999</v>
+      </c>
+      <c r="P55">
+        <v>1.657881216</v>
+      </c>
+      <c r="Q55">
+        <v>9.357881215999999</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.09424916039493925</v>
+      </c>
+      <c r="T55">
+        <v>1.205416530324766</v>
+      </c>
+      <c r="U55">
+        <v>0.0912</v>
+      </c>
+      <c r="V55">
+        <v>0.28</v>
+      </c>
+      <c r="W55">
+        <v>0.065664</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>1.576029462444869</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.07928197833174669</v>
+      </c>
+      <c r="C56">
+        <v>29.43414430679827</v>
+      </c>
+      <c r="D56">
+        <v>69.79214430679828</v>
+      </c>
+      <c r="E56">
+        <v>16.158</v>
+      </c>
+      <c r="F56">
+        <v>44.658</v>
+      </c>
+      <c r="G56">
+        <v>4.3</v>
+      </c>
+      <c r="H56">
+        <v>54.2</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>14</v>
+      </c>
+      <c r="K56">
+        <v>7.7</v>
+      </c>
+      <c r="L56">
+        <v>6.3</v>
+      </c>
+      <c r="M56">
+        <v>4.0728096</v>
+      </c>
+      <c r="N56">
+        <v>2.2271904</v>
+      </c>
+      <c r="O56">
+        <v>0.6236133119999999</v>
+      </c>
+      <c r="P56">
+        <v>1.603577088</v>
+      </c>
+      <c r="Q56">
+        <v>9.303577088000001</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.09526830072118847</v>
+      </c>
+      <c r="T56">
+        <v>1.227571754808445</v>
+      </c>
+      <c r="U56">
+        <v>0.0912</v>
+      </c>
+      <c r="V56">
+        <v>0.28</v>
+      </c>
+      <c r="W56">
+        <v>0.065664</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>1.546843731658853</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.07946493127787194</v>
+      </c>
+      <c r="C57">
+        <v>28.51397689874539</v>
+      </c>
+      <c r="D57">
+        <v>69.6989768987454</v>
+      </c>
+      <c r="E57">
+        <v>16.98500000000001</v>
+      </c>
+      <c r="F57">
+        <v>45.48500000000001</v>
+      </c>
+      <c r="G57">
+        <v>4.3</v>
+      </c>
+      <c r="H57">
+        <v>54.2</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>14</v>
+      </c>
+      <c r="K57">
+        <v>7.7</v>
+      </c>
+      <c r="L57">
+        <v>6.3</v>
+      </c>
+      <c r="M57">
+        <v>4.148232000000001</v>
+      </c>
+      <c r="N57">
+        <v>2.151767999999999</v>
+      </c>
+      <c r="O57">
+        <v>0.6024950399999998</v>
+      </c>
+      <c r="P57">
+        <v>1.549272959999999</v>
+      </c>
+      <c r="Q57">
+        <v>9.249272959999999</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.09633273617304877</v>
+      </c>
+      <c r="T57">
+        <v>1.250711655935843</v>
+      </c>
+      <c r="U57">
+        <v>0.0912</v>
+      </c>
+      <c r="V57">
+        <v>0.28</v>
+      </c>
+      <c r="W57">
+        <v>0.065664</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>1.518719300174146</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1098721149746053</v>
+      </c>
+      <c r="C58">
+        <v>15.03097742948189</v>
+      </c>
+      <c r="D58">
+        <v>57.04297742948189</v>
+      </c>
+      <c r="E58">
+        <v>17.812</v>
+      </c>
+      <c r="F58">
+        <v>46.312</v>
+      </c>
+      <c r="G58">
+        <v>4.3</v>
+      </c>
+      <c r="H58">
+        <v>54.2</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>14</v>
+      </c>
+      <c r="K58">
+        <v>7.7</v>
+      </c>
+      <c r="L58">
+        <v>6.3</v>
+      </c>
+      <c r="M58">
+        <v>7.252459200000001</v>
+      </c>
+      <c r="N58">
+        <v>-0.9524592000000016</v>
+      </c>
+      <c r="O58">
+        <v>-0.2666885760000005</v>
+      </c>
+      <c r="P58">
+        <v>-0.6857706240000012</v>
+      </c>
+      <c r="Q58">
+        <v>7.014229375999999</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.09887778136747988</v>
+      </c>
+      <c r="T58">
+        <v>1.306038725379997</v>
+      </c>
+      <c r="U58">
+        <v>0.1566</v>
+      </c>
+      <c r="V58">
+        <v>0.2432278419435989</v>
+      </c>
+      <c r="W58">
+        <v>0.1185105199516324</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.8686708640842817</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1110501149746053</v>
+      </c>
+      <c r="C59">
+        <v>13.80550623394203</v>
+      </c>
+      <c r="D59">
+        <v>56.64450623394205</v>
+      </c>
+      <c r="E59">
+        <v>18.63900000000001</v>
+      </c>
+      <c r="F59">
+        <v>47.13900000000001</v>
+      </c>
+      <c r="G59">
+        <v>4.3</v>
+      </c>
+      <c r="H59">
+        <v>54.2</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>14</v>
+      </c>
+      <c r="K59">
+        <v>7.7</v>
+      </c>
+      <c r="L59">
+        <v>6.3</v>
+      </c>
+      <c r="M59">
+        <v>7.381967400000002</v>
+      </c>
+      <c r="N59">
+        <v>-1.081967400000003</v>
+      </c>
+      <c r="O59">
+        <v>-0.3029508720000008</v>
+      </c>
+      <c r="P59">
+        <v>-0.7790165280000019</v>
+      </c>
+      <c r="Q59">
+        <v>6.920983471999998</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1002749390737004</v>
+      </c>
+      <c r="T59">
+        <v>1.336411718993486</v>
+      </c>
+      <c r="U59">
+        <v>0.1566</v>
+      </c>
+      <c r="V59">
+        <v>0.2389606868217813</v>
+      </c>
+      <c r="W59">
+        <v>0.1191787564437091</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.8534310243635047</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1122281149746053</v>
+      </c>
+      <c r="C60">
+        <v>12.58556342591594</v>
+      </c>
+      <c r="D60">
+        <v>56.25156342591594</v>
+      </c>
+      <c r="E60">
+        <v>19.466</v>
+      </c>
+      <c r="F60">
+        <v>47.966</v>
+      </c>
+      <c r="G60">
+        <v>4.3</v>
+      </c>
+      <c r="H60">
+        <v>54.2</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>14</v>
+      </c>
+      <c r="K60">
+        <v>7.7</v>
+      </c>
+      <c r="L60">
+        <v>6.3</v>
+      </c>
+      <c r="M60">
+        <v>7.511475600000001</v>
+      </c>
+      <c r="N60">
+        <v>-1.211475600000001</v>
+      </c>
+      <c r="O60">
+        <v>-0.3392131680000003</v>
+      </c>
+      <c r="P60">
+        <v>-0.8722624320000005</v>
+      </c>
+      <c r="Q60">
+        <v>6.827737568</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1017386280992646</v>
+      </c>
+      <c r="T60">
+        <v>1.368231045636187</v>
+      </c>
+      <c r="U60">
+        <v>0.1566</v>
+      </c>
+      <c r="V60">
+        <v>0.2348406749800266</v>
+      </c>
+      <c r="W60">
+        <v>0.1198239502981279</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.8387166963572377</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1134061149746053</v>
+      </c>
+      <c r="C61">
+        <v>11.3710347467814</v>
+      </c>
+      <c r="D61">
+        <v>55.86403474678141</v>
+      </c>
+      <c r="E61">
+        <v>20.293</v>
+      </c>
+      <c r="F61">
+        <v>48.793</v>
+      </c>
+      <c r="G61">
+        <v>4.3</v>
+      </c>
+      <c r="H61">
+        <v>54.2</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>14</v>
+      </c>
+      <c r="K61">
+        <v>7.7</v>
+      </c>
+      <c r="L61">
+        <v>6.3</v>
+      </c>
+      <c r="M61">
+        <v>7.640983800000001</v>
+      </c>
+      <c r="N61">
+        <v>-1.340983800000001</v>
+      </c>
+      <c r="O61">
+        <v>-0.3754754640000003</v>
+      </c>
+      <c r="P61">
+        <v>-0.9655083360000006</v>
+      </c>
+      <c r="Q61">
+        <v>6.734491663999999</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1032737165894906</v>
+      </c>
+      <c r="T61">
+        <v>1.401602534554143</v>
+      </c>
+      <c r="U61">
+        <v>0.1566</v>
+      </c>
+      <c r="V61">
+        <v>0.2308603245566363</v>
+      </c>
+      <c r="W61">
+        <v>0.1204472731744308</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.8245011591308438</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1145841149746053</v>
+      </c>
+      <c r="C62">
+        <v>10.16180906497858</v>
+      </c>
+      <c r="D62">
+        <v>55.48180906497858</v>
+      </c>
+      <c r="E62">
+        <v>21.12</v>
+      </c>
+      <c r="F62">
+        <v>49.62</v>
+      </c>
+      <c r="G62">
+        <v>4.3</v>
+      </c>
+      <c r="H62">
+        <v>54.2</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>14</v>
+      </c>
+      <c r="K62">
+        <v>7.7</v>
+      </c>
+      <c r="L62">
+        <v>6.3</v>
+      </c>
+      <c r="M62">
+        <v>7.770492000000001</v>
+      </c>
+      <c r="N62">
+        <v>-1.470492000000001</v>
+      </c>
+      <c r="O62">
+        <v>-0.4117377600000003</v>
+      </c>
+      <c r="P62">
+        <v>-1.058754240000001</v>
+      </c>
+      <c r="Q62">
+        <v>6.641245759999999</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1048855595042279</v>
+      </c>
+      <c r="T62">
+        <v>1.436642597917997</v>
+      </c>
+      <c r="U62">
+        <v>0.1566</v>
+      </c>
+      <c r="V62">
+        <v>0.2270126524806923</v>
+      </c>
+      <c r="W62">
+        <v>0.1210498186215236</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.8107594731453297</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1486461888344283</v>
+      </c>
+      <c r="C63">
+        <v>0.1712267533599174</v>
+      </c>
+      <c r="D63">
+        <v>46.31822675335992</v>
+      </c>
+      <c r="E63">
+        <v>21.947</v>
+      </c>
+      <c r="F63">
+        <v>50.447</v>
+      </c>
+      <c r="G63">
+        <v>4.3</v>
+      </c>
+      <c r="H63">
+        <v>54.2</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>14</v>
+      </c>
+      <c r="K63">
+        <v>7.7</v>
+      </c>
+      <c r="L63">
+        <v>6.3</v>
+      </c>
+      <c r="M63">
+        <v>10.5333336</v>
+      </c>
+      <c r="N63">
+        <v>-4.233333600000001</v>
+      </c>
+      <c r="O63">
+        <v>-1.185333408</v>
+      </c>
+      <c r="P63">
+        <v>-3.048000192</v>
+      </c>
+      <c r="Q63">
+        <v>4.651999807999999</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1092520452859339</v>
+      </c>
+      <c r="T63">
+        <v>1.531566201868127</v>
+      </c>
+      <c r="U63">
+        <v>0.2088</v>
+      </c>
+      <c r="V63">
+        <v>0.1674683501906747</v>
+      </c>
+      <c r="W63">
+        <v>0.1738326084801871</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.598101250680981</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1503461888344284</v>
+      </c>
+      <c r="C64">
+        <v>-1.034459165886361</v>
+      </c>
+      <c r="D64">
+        <v>45.93954083411364</v>
+      </c>
+      <c r="E64">
+        <v>22.774</v>
+      </c>
+      <c r="F64">
+        <v>51.274</v>
+      </c>
+      <c r="G64">
+        <v>4.3</v>
+      </c>
+      <c r="H64">
+        <v>54.2</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>14</v>
+      </c>
+      <c r="K64">
+        <v>7.7</v>
+      </c>
+      <c r="L64">
+        <v>6.3</v>
+      </c>
+      <c r="M64">
+        <v>10.7060112</v>
+      </c>
+      <c r="N64">
+        <v>-4.406011200000001</v>
+      </c>
+      <c r="O64">
+        <v>-1.233683136</v>
+      </c>
+      <c r="P64">
+        <v>-3.172328064</v>
+      </c>
+      <c r="Q64">
+        <v>4.527671936</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.111106046477669</v>
+      </c>
+      <c r="T64">
+        <v>1.571870575601499</v>
+      </c>
+      <c r="U64">
+        <v>0.2088</v>
+      </c>
+      <c r="V64">
+        <v>0.1647672477682444</v>
+      </c>
+      <c r="W64">
+        <v>0.1743965986659906</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.5884544563151587</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1520461888344284</v>
+      </c>
+      <c r="C65">
+        <v>-2.234003221903215</v>
+      </c>
+      <c r="D65">
+        <v>45.56699677809679</v>
+      </c>
+      <c r="E65">
+        <v>23.601</v>
+      </c>
+      <c r="F65">
+        <v>52.101</v>
+      </c>
+      <c r="G65">
+        <v>4.3</v>
+      </c>
+      <c r="H65">
+        <v>54.2</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>14</v>
+      </c>
+      <c r="K65">
+        <v>7.7</v>
+      </c>
+      <c r="L65">
+        <v>6.3</v>
+      </c>
+      <c r="M65">
+        <v>10.8786888</v>
+      </c>
+      <c r="N65">
+        <v>-4.578688800000001</v>
+      </c>
+      <c r="O65">
+        <v>-1.282032864</v>
+      </c>
+      <c r="P65">
+        <v>-3.296655936000001</v>
+      </c>
+      <c r="Q65">
+        <v>4.403344064</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1130602639500384</v>
+      </c>
+      <c r="T65">
+        <v>1.614353564131269</v>
+      </c>
+      <c r="U65">
+        <v>0.2088</v>
+      </c>
+      <c r="V65">
+        <v>0.162151894629066</v>
+      </c>
+      <c r="W65">
+        <v>0.174942684401451</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.5791139093895212</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1537461888344284</v>
+      </c>
+      <c r="C66">
+        <v>-3.42755363397152</v>
+      </c>
+      <c r="D66">
+        <v>45.20044636602849</v>
+      </c>
+      <c r="E66">
+        <v>24.428</v>
+      </c>
+      <c r="F66">
+        <v>52.928</v>
+      </c>
+      <c r="G66">
+        <v>4.3</v>
+      </c>
+      <c r="H66">
+        <v>54.2</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>14</v>
+      </c>
+      <c r="K66">
+        <v>7.7</v>
+      </c>
+      <c r="L66">
+        <v>6.3</v>
+      </c>
+      <c r="M66">
+        <v>11.0513664</v>
+      </c>
+      <c r="N66">
+        <v>-4.751366400000001</v>
+      </c>
+      <c r="O66">
+        <v>-1.330382592000001</v>
+      </c>
+      <c r="P66">
+        <v>-3.420983808000001</v>
+      </c>
+      <c r="Q66">
+        <v>4.279016191999999</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1151230490597617</v>
+      </c>
+      <c r="T66">
+        <v>1.659196718690471</v>
+      </c>
+      <c r="U66">
+        <v>0.2088</v>
+      </c>
+      <c r="V66">
+        <v>0.1596182712754868</v>
+      </c>
+      <c r="W66">
+        <v>0.1754717049576784</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.57006525455531</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1554461888344284</v>
+      </c>
+      <c r="C67">
+        <v>-4.615253890203554</v>
+      </c>
+      <c r="D67">
+        <v>44.83974610979645</v>
+      </c>
+      <c r="E67">
+        <v>25.255</v>
+      </c>
+      <c r="F67">
+        <v>53.755</v>
+      </c>
+      <c r="G67">
+        <v>4.3</v>
+      </c>
+      <c r="H67">
+        <v>54.2</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>14</v>
+      </c>
+      <c r="K67">
+        <v>7.7</v>
+      </c>
+      <c r="L67">
+        <v>6.3</v>
+      </c>
+      <c r="M67">
+        <v>11.224044</v>
+      </c>
+      <c r="N67">
+        <v>-4.924044000000001</v>
+      </c>
+      <c r="O67">
+        <v>-1.378732320000001</v>
+      </c>
+      <c r="P67">
+        <v>-3.545311680000001</v>
+      </c>
+      <c r="Q67">
+        <v>4.15468832</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1173037076043263</v>
+      </c>
+      <c r="T67">
+        <v>1.706602339224485</v>
+      </c>
+      <c r="U67">
+        <v>0.2088</v>
+      </c>
+      <c r="V67">
+        <v>0.1571626055635562</v>
+      </c>
+      <c r="W67">
+        <v>0.1759844479583295</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.5612950198698436</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1571461888344284</v>
+      </c>
+      <c r="C68">
+        <v>-5.79724293482257</v>
+      </c>
+      <c r="D68">
+        <v>44.48475706517744</v>
+      </c>
+      <c r="E68">
+        <v>26.08200000000001</v>
+      </c>
+      <c r="F68">
+        <v>54.58200000000001</v>
+      </c>
+      <c r="G68">
+        <v>4.3</v>
+      </c>
+      <c r="H68">
+        <v>54.2</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>14</v>
+      </c>
+      <c r="K68">
+        <v>7.7</v>
+      </c>
+      <c r="L68">
+        <v>6.3</v>
+      </c>
+      <c r="M68">
+        <v>11.3967216</v>
+      </c>
+      <c r="N68">
+        <v>-5.096721600000003</v>
+      </c>
+      <c r="O68">
+        <v>-1.427082048000001</v>
+      </c>
+      <c r="P68">
+        <v>-3.669639552000002</v>
+      </c>
+      <c r="Q68">
+        <v>4.030360447999998</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1196126401809241</v>
+      </c>
+      <c r="T68">
+        <v>1.756796525672264</v>
+      </c>
+      <c r="U68">
+        <v>0.2088</v>
+      </c>
+      <c r="V68">
+        <v>0.1547813539641084</v>
+      </c>
+      <c r="W68">
+        <v>0.1764816532922942</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.5527905498718156</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1588461888344284</v>
+      </c>
+      <c r="C69">
+        <v>-6.973655346616141</v>
+      </c>
+      <c r="D69">
+        <v>44.13534465338387</v>
+      </c>
+      <c r="E69">
+        <v>26.90900000000001</v>
+      </c>
+      <c r="F69">
+        <v>55.40900000000001</v>
+      </c>
+      <c r="G69">
+        <v>4.3</v>
+      </c>
+      <c r="H69">
+        <v>54.2</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>14</v>
+      </c>
+      <c r="K69">
+        <v>7.7</v>
+      </c>
+      <c r="L69">
+        <v>6.3</v>
+      </c>
+      <c r="M69">
+        <v>11.5693992</v>
+      </c>
+      <c r="N69">
+        <v>-5.269399200000001</v>
+      </c>
+      <c r="O69">
+        <v>-1.475431776000001</v>
+      </c>
+      <c r="P69">
+        <v>-3.793967424000001</v>
+      </c>
+      <c r="Q69">
+        <v>3.906032575999999</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1220615080651946</v>
+      </c>
+      <c r="T69">
+        <v>1.810032784025969</v>
+      </c>
+      <c r="U69">
+        <v>0.2088</v>
+      </c>
+      <c r="V69">
+        <v>0.1524711845019575</v>
+      </c>
+      <c r="W69">
+        <v>0.1769640166759913</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.5445399446498482</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1605461888344284</v>
+      </c>
+      <c r="C70">
+        <v>-8.14462150904501</v>
+      </c>
+      <c r="D70">
+        <v>43.791378490955</v>
+      </c>
+      <c r="E70">
+        <v>27.736</v>
+      </c>
+      <c r="F70">
+        <v>56.236</v>
+      </c>
+      <c r="G70">
+        <v>4.3</v>
+      </c>
+      <c r="H70">
+        <v>54.2</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>14</v>
+      </c>
+      <c r="K70">
+        <v>7.7</v>
+      </c>
+      <c r="L70">
+        <v>6.3</v>
+      </c>
+      <c r="M70">
+        <v>11.7420768</v>
+      </c>
+      <c r="N70">
+        <v>-5.442076800000001</v>
+      </c>
+      <c r="O70">
+        <v>-1.523781504</v>
+      </c>
+      <c r="P70">
+        <v>-3.918295296000001</v>
+      </c>
+      <c r="Q70">
+        <v>3.781704703999999</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1246634301922319</v>
+      </c>
+      <c r="T70">
+        <v>1.86659630852678</v>
+      </c>
+      <c r="U70">
+        <v>0.2088</v>
+      </c>
+      <c r="V70">
+        <v>0.1502289612004581</v>
+      </c>
+      <c r="W70">
+        <v>0.1774321929013443</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.5365320042873505</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1622461888344284</v>
+      </c>
+      <c r="C71">
+        <v>-9.310267772458992</v>
+      </c>
+      <c r="D71">
+        <v>43.45273222754102</v>
+      </c>
+      <c r="E71">
+        <v>28.56300000000001</v>
+      </c>
+      <c r="F71">
+        <v>57.06300000000001</v>
+      </c>
+      <c r="G71">
+        <v>4.3</v>
+      </c>
+      <c r="H71">
+        <v>54.2</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>14</v>
+      </c>
+      <c r="K71">
+        <v>7.7</v>
+      </c>
+      <c r="L71">
+        <v>6.3</v>
+      </c>
+      <c r="M71">
+        <v>11.9147544</v>
+      </c>
+      <c r="N71">
+        <v>-5.614754400000003</v>
+      </c>
+      <c r="O71">
+        <v>-1.572131232000001</v>
+      </c>
+      <c r="P71">
+        <v>-4.042623168000002</v>
+      </c>
+      <c r="Q71">
+        <v>3.657376831999998</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1274332182629491</v>
+      </c>
+      <c r="T71">
+        <v>1.926809092672806</v>
+      </c>
+      <c r="U71">
+        <v>0.2088</v>
+      </c>
+      <c r="V71">
+        <v>0.1480517298787123</v>
+      </c>
+      <c r="W71">
+        <v>0.1778867988013249</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.5287561781382584</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1639461888344284</v>
+      </c>
+      <c r="C72">
+        <v>-10.47071660884397</v>
+      </c>
+      <c r="D72">
+        <v>43.11928339115604</v>
+      </c>
+      <c r="E72">
+        <v>29.39000000000001</v>
+      </c>
+      <c r="F72">
+        <v>57.89000000000001</v>
+      </c>
+      <c r="G72">
+        <v>4.3</v>
+      </c>
+      <c r="H72">
+        <v>54.2</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>14</v>
+      </c>
+      <c r="K72">
+        <v>7.7</v>
+      </c>
+      <c r="L72">
+        <v>6.3</v>
+      </c>
+      <c r="M72">
+        <v>12.087432</v>
+      </c>
+      <c r="N72">
+        <v>-5.787432000000002</v>
+      </c>
+      <c r="O72">
+        <v>-1.620480960000001</v>
+      </c>
+      <c r="P72">
+        <v>-4.166951040000001</v>
+      </c>
+      <c r="Q72">
+        <v>3.533048959999999</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.130387658871714</v>
+      </c>
+      <c r="T72">
+        <v>1.991036062428566</v>
+      </c>
+      <c r="U72">
+        <v>0.2088</v>
+      </c>
+      <c r="V72">
+        <v>0.1459367051661594</v>
+      </c>
+      <c r="W72">
+        <v>0.1783284159613059</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.5212025184505691</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.1656461888344284</v>
+      </c>
+      <c r="C73">
+        <v>-11.62608675949823</v>
+      </c>
+      <c r="D73">
+        <v>42.79091324050177</v>
+      </c>
+      <c r="E73">
+        <v>30.217</v>
+      </c>
+      <c r="F73">
+        <v>58.717</v>
+      </c>
+      <c r="G73">
+        <v>4.3</v>
+      </c>
+      <c r="H73">
+        <v>54.2</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>14</v>
+      </c>
+      <c r="K73">
+        <v>7.7</v>
+      </c>
+      <c r="L73">
+        <v>6.3</v>
+      </c>
+      <c r="M73">
+        <v>12.2601096</v>
+      </c>
+      <c r="N73">
+        <v>-5.9601096</v>
+      </c>
+      <c r="O73">
+        <v>-1.668830688</v>
+      </c>
+      <c r="P73">
+        <v>-4.291278912</v>
+      </c>
+      <c r="Q73">
+        <v>3.408721088</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1335458540052214</v>
+      </c>
+      <c r="T73">
+        <v>2.059692478374378</v>
+      </c>
+      <c r="U73">
+        <v>0.2088</v>
+      </c>
+      <c r="V73">
+        <v>0.1438812586145233</v>
+      </c>
+      <c r="W73">
+        <v>0.1787575932012876</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.5138616379090118</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.1673461888344283</v>
+      </c>
+      <c r="C74">
+        <v>-12.77649337601191</v>
+      </c>
+      <c r="D74">
+        <v>42.46750662398809</v>
+      </c>
+      <c r="E74">
+        <v>31.044</v>
+      </c>
+      <c r="F74">
+        <v>59.544</v>
+      </c>
+      <c r="G74">
+        <v>4.3</v>
+      </c>
+      <c r="H74">
+        <v>54.2</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>14</v>
+      </c>
+      <c r="K74">
+        <v>7.7</v>
+      </c>
+      <c r="L74">
+        <v>6.3</v>
+      </c>
+      <c r="M74">
+        <v>12.4327872</v>
+      </c>
+      <c r="N74">
+        <v>-6.1327872</v>
+      </c>
+      <c r="O74">
+        <v>-1.717180416</v>
+      </c>
+      <c r="P74">
+        <v>-4.415606784</v>
+      </c>
+      <c r="Q74">
+        <v>3.284393216000001</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.1369296345054078</v>
+      </c>
+      <c r="T74">
+        <v>2.133252924030606</v>
+      </c>
+      <c r="U74">
+        <v>0.2088</v>
+      </c>
+      <c r="V74">
+        <v>0.1418829078004328</v>
+      </c>
+      <c r="W74">
+        <v>0.1791748488512696</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.506724670715831</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.1913389302388843</v>
+      </c>
+      <c r="C75">
+        <v>-17.69674339626509</v>
+      </c>
+      <c r="D75">
+        <v>38.37425660373491</v>
+      </c>
+      <c r="E75">
+        <v>31.871</v>
+      </c>
+      <c r="F75">
+        <v>60.371</v>
+      </c>
+      <c r="G75">
+        <v>4.3</v>
+      </c>
+      <c r="H75">
+        <v>54.2</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>14</v>
+      </c>
+      <c r="K75">
+        <v>7.7</v>
+      </c>
+      <c r="L75">
+        <v>6.3</v>
+      </c>
+      <c r="M75">
+        <v>14.4165948</v>
+      </c>
+      <c r="N75">
+        <v>-8.116594800000001</v>
+      </c>
+      <c r="O75">
+        <v>-2.272646544000001</v>
+      </c>
+      <c r="P75">
+        <v>-5.843948256000001</v>
+      </c>
+      <c r="Q75">
+        <v>1.856051743999999</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.1420186632072968</v>
+      </c>
+      <c r="T75">
+        <v>2.243883982767321</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.1223589914589262</v>
+      </c>
+      <c r="W75">
+        <v>0.2095806728396084</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.4369963980675936</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.1933389302388843</v>
+      </c>
+      <c r="C76">
+        <v>-18.82960586459876</v>
+      </c>
+      <c r="D76">
+        <v>38.06839413540124</v>
+      </c>
+      <c r="E76">
+        <v>32.698</v>
+      </c>
+      <c r="F76">
+        <v>61.198</v>
+      </c>
+      <c r="G76">
+        <v>4.3</v>
+      </c>
+      <c r="H76">
+        <v>54.2</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>14</v>
+      </c>
+      <c r="K76">
+        <v>7.7</v>
+      </c>
+      <c r="L76">
+        <v>6.3</v>
+      </c>
+      <c r="M76">
+        <v>14.6140824</v>
+      </c>
+      <c r="N76">
+        <v>-8.3140824</v>
+      </c>
+      <c r="O76">
+        <v>-2.327943072</v>
+      </c>
+      <c r="P76">
+        <v>-5.986139328</v>
+      </c>
+      <c r="Q76">
+        <v>1.713860672</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.1459886117921928</v>
+      </c>
+      <c r="T76">
+        <v>2.330187212873756</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.1207054915743461</v>
+      </c>
+      <c r="W76">
+        <v>0.2099755286120461</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.4310910413369504</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.1953389302388843</v>
+      </c>
+      <c r="C77">
+        <v>-19.95763112706134</v>
+      </c>
+      <c r="D77">
+        <v>37.76736887293867</v>
+      </c>
+      <c r="E77">
+        <v>33.52500000000001</v>
+      </c>
+      <c r="F77">
+        <v>62.02500000000001</v>
+      </c>
+      <c r="G77">
+        <v>4.3</v>
+      </c>
+      <c r="H77">
+        <v>54.2</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>14</v>
+      </c>
+      <c r="K77">
+        <v>7.7</v>
+      </c>
+      <c r="L77">
+        <v>6.3</v>
+      </c>
+      <c r="M77">
+        <v>14.81157</v>
+      </c>
+      <c r="N77">
+        <v>-8.511570000000003</v>
+      </c>
+      <c r="O77">
+        <v>-2.383239600000001</v>
+      </c>
+      <c r="P77">
+        <v>-6.128330400000001</v>
+      </c>
+      <c r="Q77">
+        <v>1.571669599999999</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.1502761562638805</v>
+      </c>
+      <c r="T77">
+        <v>2.423394701388707</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.1190960850200215</v>
+      </c>
+      <c r="W77">
+        <v>0.2103598548972189</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.425343160785791</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.1973389302388843</v>
+      </c>
+      <c r="C78">
+        <v>-21.08093303378579</v>
+      </c>
+      <c r="D78">
+        <v>37.47106696621422</v>
+      </c>
+      <c r="E78">
+        <v>34.352</v>
+      </c>
+      <c r="F78">
+        <v>62.852</v>
+      </c>
+      <c r="G78">
+        <v>4.3</v>
+      </c>
+      <c r="H78">
+        <v>54.2</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>14</v>
+      </c>
+      <c r="K78">
+        <v>7.7</v>
+      </c>
+      <c r="L78">
+        <v>6.3</v>
+      </c>
+      <c r="M78">
+        <v>15.0090576</v>
+      </c>
+      <c r="N78">
+        <v>-8.709057600000001</v>
+      </c>
+      <c r="O78">
+        <v>-2.438536128</v>
+      </c>
+      <c r="P78">
+        <v>-6.270521472</v>
+      </c>
+      <c r="Q78">
+        <v>1.429478528</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.1549209961082089</v>
+      </c>
+      <c r="T78">
+        <v>2.524369480613236</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.1175290312697581</v>
+      </c>
+      <c r="W78">
+        <v>0.2107340673327818</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.4197465402491359</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.1993389302388843</v>
+      </c>
+      <c r="C79">
+        <v>-22.19962188989636</v>
+      </c>
+      <c r="D79">
+        <v>37.17937811010365</v>
+      </c>
+      <c r="E79">
+        <v>35.179</v>
+      </c>
+      <c r="F79">
+        <v>63.679</v>
+      </c>
+      <c r="G79">
+        <v>4.3</v>
+      </c>
+      <c r="H79">
+        <v>54.2</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>14</v>
+      </c>
+      <c r="K79">
+        <v>7.7</v>
+      </c>
+      <c r="L79">
+        <v>6.3</v>
+      </c>
+      <c r="M79">
+        <v>15.2065452</v>
+      </c>
+      <c r="N79">
+        <v>-8.9065452</v>
+      </c>
+      <c r="O79">
+        <v>-2.493832656</v>
+      </c>
+      <c r="P79">
+        <v>-6.412712544</v>
+      </c>
+      <c r="Q79">
+        <v>1.287287456</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.1599697350694353</v>
+      </c>
+      <c r="T79">
+        <v>2.634124675422508</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.1160026802143067</v>
+      </c>
+      <c r="W79">
+        <v>0.2110985599648236</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.4142952864796667</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2013389302388843</v>
+      </c>
+      <c r="C80">
+        <v>-23.31380459242112</v>
+      </c>
+      <c r="D80">
+        <v>36.89219540757888</v>
+      </c>
+      <c r="E80">
+        <v>36.006</v>
+      </c>
+      <c r="F80">
+        <v>64.506</v>
+      </c>
+      <c r="G80">
+        <v>4.3</v>
+      </c>
+      <c r="H80">
+        <v>54.2</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>14</v>
+      </c>
+      <c r="K80">
+        <v>7.7</v>
+      </c>
+      <c r="L80">
+        <v>6.3</v>
+      </c>
+      <c r="M80">
+        <v>15.4040328</v>
+      </c>
+      <c r="N80">
+        <v>-9.104032800000002</v>
+      </c>
+      <c r="O80">
+        <v>-2.549129184000001</v>
+      </c>
+      <c r="P80">
+        <v>-6.554903616000002</v>
+      </c>
+      <c r="Q80">
+        <v>1.145096383999999</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.1654774502998642</v>
+      </c>
+      <c r="T80">
+        <v>2.75385761521444</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.1145154663654053</v>
+      </c>
+      <c r="W80">
+        <v>0.2114537066319412</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.408983808447876</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2033389302388843</v>
+      </c>
+      <c r="C81">
+        <v>-24.42358476090804</v>
+      </c>
+      <c r="D81">
+        <v>36.60941523909196</v>
+      </c>
+      <c r="E81">
+        <v>36.833</v>
+      </c>
+      <c r="F81">
+        <v>65.333</v>
+      </c>
+      <c r="G81">
+        <v>4.3</v>
+      </c>
+      <c r="H81">
+        <v>54.2</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>14</v>
+      </c>
+      <c r="K81">
+        <v>7.7</v>
+      </c>
+      <c r="L81">
+        <v>6.3</v>
+      </c>
+      <c r="M81">
+        <v>15.6015204</v>
+      </c>
+      <c r="N81">
+        <v>-9.301520400000001</v>
+      </c>
+      <c r="O81">
+        <v>-2.604425712000001</v>
+      </c>
+      <c r="P81">
+        <v>-6.697094688</v>
+      </c>
+      <c r="Q81">
+        <v>1.002905312</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.171509709837953</v>
+      </c>
+      <c r="T81">
+        <v>2.884993692129413</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.1130659035000204</v>
+      </c>
+      <c r="W81">
+        <v>0.2117998622441951</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.4038067982143586</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2053389302388843</v>
+      </c>
+      <c r="C82">
+        <v>-25.5290628620795</v>
+      </c>
+      <c r="D82">
+        <v>36.33093713792051</v>
+      </c>
+      <c r="E82">
+        <v>37.66000000000001</v>
+      </c>
+      <c r="F82">
+        <v>66.16000000000001</v>
+      </c>
+      <c r="G82">
+        <v>4.3</v>
+      </c>
+      <c r="H82">
+        <v>54.2</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>14</v>
+      </c>
+      <c r="K82">
+        <v>7.7</v>
+      </c>
+      <c r="L82">
+        <v>6.3</v>
+      </c>
+      <c r="M82">
+        <v>15.799008</v>
+      </c>
+      <c r="N82">
+        <v>-9.499008000000003</v>
+      </c>
+      <c r="O82">
+        <v>-2.659722240000001</v>
+      </c>
+      <c r="P82">
+        <v>-6.839285760000003</v>
+      </c>
+      <c r="Q82">
+        <v>0.8607142399999974</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.1781451953298507</v>
+      </c>
+      <c r="T82">
+        <v>3.029243376735884</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.1116525797062702</v>
+      </c>
+      <c r="W82">
+        <v>0.2121373639661427</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.3987592132366791</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2073389302388843</v>
+      </c>
+      <c r="C83">
+        <v>-26.6303363288406</v>
+      </c>
+      <c r="D83">
+        <v>36.05666367115941</v>
+      </c>
+      <c r="E83">
+        <v>38.48700000000001</v>
+      </c>
+      <c r="F83">
+        <v>66.98700000000001</v>
+      </c>
+      <c r="G83">
+        <v>4.3</v>
+      </c>
+      <c r="H83">
+        <v>54.2</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>14</v>
+      </c>
+      <c r="K83">
+        <v>7.7</v>
+      </c>
+      <c r="L83">
+        <v>6.3</v>
+      </c>
+      <c r="M83">
+        <v>15.9964956</v>
+      </c>
+      <c r="N83">
+        <v>-9.696495600000002</v>
+      </c>
+      <c r="O83">
+        <v>-2.715018768000001</v>
+      </c>
+      <c r="P83">
+        <v>-6.981476832000001</v>
+      </c>
+      <c r="Q83">
+        <v>0.718523167999999</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.1854791529787902</v>
+      </c>
+      <c r="T83">
+        <v>3.188677238669352</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.1102741527963162</v>
+      </c>
+      <c r="W83">
+        <v>0.2124665323122397</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.3938362599868436</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2093389302388843</v>
+      </c>
+      <c r="C84">
+        <v>-27.72749967393723</v>
+      </c>
+      <c r="D84">
+        <v>35.78650032606278</v>
+      </c>
+      <c r="E84">
+        <v>39.31400000000001</v>
+      </c>
+      <c r="F84">
+        <v>67.81400000000001</v>
+      </c>
+      <c r="G84">
+        <v>4.3</v>
+      </c>
+      <c r="H84">
+        <v>54.2</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>14</v>
+      </c>
+      <c r="K84">
+        <v>7.7</v>
+      </c>
+      <c r="L84">
+        <v>6.3</v>
+      </c>
+      <c r="M84">
+        <v>16.1939832</v>
+      </c>
+      <c r="N84">
+        <v>-9.893983200000001</v>
+      </c>
+      <c r="O84">
+        <v>-2.770315296000001</v>
+      </c>
+      <c r="P84">
+        <v>-7.123667904</v>
+      </c>
+      <c r="Q84">
+        <v>0.5763320959999998</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.1936279948109452</v>
+      </c>
+      <c r="T84">
+        <v>3.365825974150983</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.1089293460548977</v>
+      </c>
+      <c r="W84">
+        <v>0.2127876721620904</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.3890333787674919</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2113389302388843</v>
+      </c>
+      <c r="C85">
+        <v>-28.82064459854252</v>
+      </c>
+      <c r="D85">
+        <v>35.52035540145749</v>
+      </c>
+      <c r="E85">
+        <v>40.14100000000001</v>
+      </c>
+      <c r="F85">
+        <v>68.64100000000001</v>
+      </c>
+      <c r="G85">
+        <v>4.3</v>
+      </c>
+      <c r="H85">
+        <v>54.2</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>14</v>
+      </c>
+      <c r="K85">
+        <v>7.7</v>
+      </c>
+      <c r="L85">
+        <v>6.3</v>
+      </c>
+      <c r="M85">
+        <v>16.3914708</v>
+      </c>
+      <c r="N85">
+        <v>-10.0914708</v>
+      </c>
+      <c r="O85">
+        <v>-2.825611824</v>
+      </c>
+      <c r="P85">
+        <v>-7.265858976</v>
+      </c>
+      <c r="Q85">
+        <v>0.4341410240000005</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.2027355239174714</v>
+      </c>
+      <c r="T85">
+        <v>3.563815737336335</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.1076169442952002</v>
+      </c>
+      <c r="W85">
+        <v>0.2131010737023062</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.3843462296257149</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2133389302388843</v>
+      </c>
+      <c r="C86">
+        <v>-29.90986009603362</v>
+      </c>
+      <c r="D86">
+        <v>35.25813990396639</v>
+      </c>
+      <c r="E86">
+        <v>40.968</v>
+      </c>
+      <c r="F86">
+        <v>69.468</v>
+      </c>
+      <c r="G86">
+        <v>4.3</v>
+      </c>
+      <c r="H86">
+        <v>54.2</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>14</v>
+      </c>
+      <c r="K86">
+        <v>7.7</v>
+      </c>
+      <c r="L86">
+        <v>6.3</v>
+      </c>
+      <c r="M86">
+        <v>16.5889584</v>
+      </c>
+      <c r="N86">
+        <v>-10.2889584</v>
+      </c>
+      <c r="O86">
+        <v>-2.880908352000001</v>
+      </c>
+      <c r="P86">
+        <v>-7.408050048000002</v>
+      </c>
+      <c r="Q86">
+        <v>0.2919499519999986</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.2129814941623133</v>
+      </c>
+      <c r="T86">
+        <v>3.786554220919854</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.1063357901964478</v>
+      </c>
+      <c r="W86">
+        <v>0.2134070133010883</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.3797706792730278</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2153389302388843</v>
+      </c>
+      <c r="C87">
+        <v>-30.99523255120567</v>
+      </c>
+      <c r="D87">
+        <v>34.99976744879433</v>
+      </c>
+      <c r="E87">
+        <v>41.795</v>
+      </c>
+      <c r="F87">
+        <v>70.295</v>
+      </c>
+      <c r="G87">
+        <v>4.3</v>
+      </c>
+      <c r="H87">
+        <v>54.2</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>14</v>
+      </c>
+      <c r="K87">
+        <v>7.7</v>
+      </c>
+      <c r="L87">
+        <v>6.3</v>
+      </c>
+      <c r="M87">
+        <v>16.786446</v>
+      </c>
+      <c r="N87">
+        <v>-10.486446</v>
+      </c>
+      <c r="O87">
+        <v>-2.93620488</v>
+      </c>
+      <c r="P87">
+        <v>-7.550241120000001</v>
+      </c>
+      <c r="Q87">
+        <v>0.1497588799999994</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.2245935937731342</v>
+      </c>
+      <c r="T87">
+        <v>4.038991168981178</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.105084780900019</v>
+      </c>
+      <c r="W87">
+        <v>0.2137057543210755</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.3753027889286392</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2173389302388843</v>
+      </c>
+      <c r="C88">
+        <v>-32.07684583515525</v>
+      </c>
+      <c r="D88">
+        <v>34.74515416484476</v>
+      </c>
+      <c r="E88">
+        <v>42.622</v>
+      </c>
+      <c r="F88">
+        <v>71.122</v>
+      </c>
+      <c r="G88">
+        <v>4.3</v>
+      </c>
+      <c r="H88">
+        <v>54.2</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>14</v>
+      </c>
+      <c r="K88">
+        <v>7.7</v>
+      </c>
+      <c r="L88">
+        <v>6.3</v>
+      </c>
+      <c r="M88">
+        <v>16.9839336</v>
+      </c>
+      <c r="N88">
+        <v>-10.6839336</v>
+      </c>
+      <c r="O88">
+        <v>-2.991501408</v>
+      </c>
+      <c r="P88">
+        <v>-7.692432192</v>
+      </c>
+      <c r="Q88">
+        <v>0.00756780800000012</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.2378645647569295</v>
+      </c>
+      <c r="T88">
+        <v>4.32749053819412</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.103862864843042</v>
+      </c>
+      <c r="W88">
+        <v>0.2139975478754816</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.3709388030108643</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2193389302388843</v>
+      </c>
+      <c r="C89">
+        <v>-33.15478139605219</v>
+      </c>
+      <c r="D89">
+        <v>34.49421860394781</v>
+      </c>
+      <c r="E89">
+        <v>43.449</v>
+      </c>
+      <c r="F89">
+        <v>71.949</v>
+      </c>
+      <c r="G89">
+        <v>4.3</v>
+      </c>
+      <c r="H89">
+        <v>54.2</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>14</v>
+      </c>
+      <c r="K89">
+        <v>7.7</v>
+      </c>
+      <c r="L89">
+        <v>6.3</v>
+      </c>
+      <c r="M89">
+        <v>17.1814212</v>
+      </c>
+      <c r="N89">
+        <v>-10.8814212</v>
+      </c>
+      <c r="O89">
+        <v>-3.046797936</v>
+      </c>
+      <c r="P89">
+        <v>-7.834623263999998</v>
+      </c>
+      <c r="Q89">
+        <v>-0.1346232639999982</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.2531772235843855</v>
+      </c>
+      <c r="T89">
+        <v>4.660374425747513</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.1026690388103634</v>
+      </c>
+      <c r="W89">
+        <v>0.2142826335320852</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.3666751386084407</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2213389302388843</v>
+      </c>
+      <c r="C90">
+        <v>-34.22911834600624</v>
+      </c>
+      <c r="D90">
+        <v>34.24688165399376</v>
+      </c>
+      <c r="E90">
+        <v>44.276</v>
+      </c>
+      <c r="F90">
+        <v>72.776</v>
+      </c>
+      <c r="G90">
+        <v>4.3</v>
+      </c>
+      <c r="H90">
+        <v>54.2</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>14</v>
+      </c>
+      <c r="K90">
+        <v>7.7</v>
+      </c>
+      <c r="L90">
+        <v>6.3</v>
+      </c>
+      <c r="M90">
+        <v>17.3789088</v>
+      </c>
+      <c r="N90">
+        <v>-11.0789088</v>
+      </c>
+      <c r="O90">
+        <v>-3.102094464</v>
+      </c>
+      <c r="P90">
+        <v>-7.976814336</v>
+      </c>
+      <c r="Q90">
+        <v>-0.2768143360000002</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.2710419922164178</v>
+      </c>
+      <c r="T90">
+        <v>5.048738961226473</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.1015023451875183</v>
+      </c>
+      <c r="W90">
+        <v>0.2145612399692206</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.3625083756697084</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2233389302388843</v>
+      </c>
+      <c r="C91">
+        <v>-35.29993354422309</v>
+      </c>
+      <c r="D91">
+        <v>34.00306645577692</v>
+      </c>
+      <c r="E91">
+        <v>45.10300000000001</v>
+      </c>
+      <c r="F91">
+        <v>73.60300000000001</v>
+      </c>
+      <c r="G91">
+        <v>4.3</v>
+      </c>
+      <c r="H91">
+        <v>54.2</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>14</v>
+      </c>
+      <c r="K91">
+        <v>7.7</v>
+      </c>
+      <c r="L91">
+        <v>6.3</v>
+      </c>
+      <c r="M91">
+        <v>17.5763964</v>
+      </c>
+      <c r="N91">
+        <v>-11.2763964</v>
+      </c>
+      <c r="O91">
+        <v>-3.157390992000001</v>
+      </c>
+      <c r="P91">
+        <v>-8.119005408000001</v>
+      </c>
+      <c r="Q91">
+        <v>-0.4190054080000012</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.2921549005997285</v>
+      </c>
+      <c r="T91">
+        <v>5.50771523042888</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.1003618693988945</v>
+      </c>
+      <c r="W91">
+        <v>0.214833585587544</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.3584352478531947</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2253389302388843</v>
+      </c>
+      <c r="C92">
+        <v>-36.3673016766334</v>
+      </c>
+      <c r="D92">
+        <v>33.76269832336661</v>
+      </c>
+      <c r="E92">
+        <v>45.93000000000001</v>
+      </c>
+      <c r="F92">
+        <v>74.43000000000001</v>
+      </c>
+      <c r="G92">
+        <v>4.3</v>
+      </c>
+      <c r="H92">
+        <v>54.2</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>14</v>
+      </c>
+      <c r="K92">
+        <v>7.7</v>
+      </c>
+      <c r="L92">
+        <v>6.3</v>
+      </c>
+      <c r="M92">
+        <v>17.773884</v>
+      </c>
+      <c r="N92">
+        <v>-11.473884</v>
+      </c>
+      <c r="O92">
+        <v>-3.212687520000001</v>
+      </c>
+      <c r="P92">
+        <v>-8.261196480000001</v>
+      </c>
+      <c r="Q92">
+        <v>-0.5611964800000004</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.3174903906597014</v>
+      </c>
+      <c r="T92">
+        <v>6.058486753471769</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.09924673751668459</v>
+      </c>
+      <c r="W92">
+        <v>0.2150998790810157</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.3544526339881593</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2273389302388843</v>
+      </c>
+      <c r="C93">
+        <v>-37.43129533216817</v>
+      </c>
+      <c r="D93">
+        <v>33.52570466783184</v>
+      </c>
+      <c r="E93">
+        <v>46.75700000000001</v>
+      </c>
+      <c r="F93">
+        <v>75.25700000000001</v>
+      </c>
+      <c r="G93">
+        <v>4.3</v>
+      </c>
+      <c r="H93">
+        <v>54.2</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>14</v>
+      </c>
+      <c r="K93">
+        <v>7.7</v>
+      </c>
+      <c r="L93">
+        <v>6.3</v>
+      </c>
+      <c r="M93">
+        <v>17.9713716</v>
+      </c>
+      <c r="N93">
+        <v>-11.6713716</v>
+      </c>
+      <c r="O93">
+        <v>-3.267984048000001</v>
+      </c>
+      <c r="P93">
+        <v>-8.403387552</v>
+      </c>
+      <c r="Q93">
+        <v>-0.7033875519999997</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.3484559896218904</v>
+      </c>
+      <c r="T93">
+        <v>6.731651948301965</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.09815611402749026</v>
+      </c>
+      <c r="W93">
+        <v>0.2153603199702353</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.3505575500981795</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2293389302388843</v>
+      </c>
+      <c r="C94">
+        <v>-38.49198507584406</v>
+      </c>
+      <c r="D94">
+        <v>33.29201492415595</v>
+      </c>
+      <c r="E94">
+        <v>47.584</v>
+      </c>
+      <c r="F94">
+        <v>76.084</v>
+      </c>
+      <c r="G94">
+        <v>4.3</v>
+      </c>
+      <c r="H94">
+        <v>54.2</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>14</v>
+      </c>
+      <c r="K94">
+        <v>7.7</v>
+      </c>
+      <c r="L94">
+        <v>6.3</v>
+      </c>
+      <c r="M94">
+        <v>18.1688592</v>
+      </c>
+      <c r="N94">
+        <v>-11.8688592</v>
+      </c>
+      <c r="O94">
+        <v>-3.323280576</v>
+      </c>
+      <c r="P94">
+        <v>-8.545578623999999</v>
+      </c>
+      <c r="Q94">
+        <v>-0.8455786239999989</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.3871629883246269</v>
+      </c>
+      <c r="T94">
+        <v>7.573108441839715</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.09708919974458276</v>
+      </c>
+      <c r="W94">
+        <v>0.2156150991009937</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.3467471419449385</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2313389302388843</v>
+      </c>
+      <c r="C95">
+        <v>-39.5494395188132</v>
+      </c>
+      <c r="D95">
+        <v>33.0615604811868</v>
+      </c>
+      <c r="E95">
+        <v>48.411</v>
+      </c>
+      <c r="F95">
+        <v>76.911</v>
+      </c>
+      <c r="G95">
+        <v>4.3</v>
+      </c>
+      <c r="H95">
+        <v>54.2</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>14</v>
+      </c>
+      <c r="K95">
+        <v>7.7</v>
+      </c>
+      <c r="L95">
+        <v>6.3</v>
+      </c>
+      <c r="M95">
+        <v>18.3663468</v>
+      </c>
+      <c r="N95">
+        <v>-12.0663468</v>
+      </c>
+      <c r="O95">
+        <v>-3.378577104000001</v>
+      </c>
+      <c r="P95">
+        <v>-8.687769696</v>
+      </c>
+      <c r="Q95">
+        <v>-0.987769696</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.4369291295138593</v>
+      </c>
+      <c r="T95">
+        <v>8.654981076388244</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.09604522985485606</v>
+      </c>
+      <c r="W95">
+        <v>0.2158643991106604</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.3430186780530573</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2333389302388843</v>
+      </c>
+      <c r="C96">
+        <v>-40.6037253855237</v>
+      </c>
+      <c r="D96">
+        <v>32.83427461447631</v>
+      </c>
+      <c r="E96">
+        <v>49.23800000000001</v>
+      </c>
+      <c r="F96">
+        <v>77.73800000000001</v>
+      </c>
+      <c r="G96">
+        <v>4.3</v>
+      </c>
+      <c r="H96">
+        <v>54.2</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>14</v>
+      </c>
+      <c r="K96">
+        <v>7.7</v>
+      </c>
+      <c r="L96">
+        <v>6.3</v>
+      </c>
+      <c r="M96">
+        <v>18.5638344</v>
+      </c>
+      <c r="N96">
+        <v>-12.2638344</v>
+      </c>
+      <c r="O96">
+        <v>-3.433873632000001</v>
+      </c>
+      <c r="P96">
+        <v>-8.829960768000003</v>
+      </c>
+      <c r="Q96">
+        <v>-1.129960768000003</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.5032839844328361</v>
+      </c>
+      <c r="T96">
+        <v>10.09747792245296</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.09502347209044268</v>
+      </c>
+      <c r="W96">
+        <v>0.2161083948648023</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.3393695431801524</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2353389302388843</v>
+      </c>
+      <c r="C97">
+        <v>-41.65490757812866</v>
+      </c>
+      <c r="D97">
+        <v>32.61009242187136</v>
+      </c>
+      <c r="E97">
+        <v>50.06500000000001</v>
+      </c>
+      <c r="F97">
+        <v>78.56500000000001</v>
+      </c>
+      <c r="G97">
+        <v>4.3</v>
+      </c>
+      <c r="H97">
+        <v>54.2</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>14</v>
+      </c>
+      <c r="K97">
+        <v>7.7</v>
+      </c>
+      <c r="L97">
+        <v>6.3</v>
+      </c>
+      <c r="M97">
+        <v>18.761322</v>
+      </c>
+      <c r="N97">
+        <v>-12.461322</v>
+      </c>
+      <c r="O97">
+        <v>-3.489170160000001</v>
+      </c>
+      <c r="P97">
+        <v>-8.972151840000002</v>
+      </c>
+      <c r="Q97">
+        <v>-1.272151840000002</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.5961807813194036</v>
+      </c>
+      <c r="T97">
+        <v>12.11697350694355</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.09402322501580644</v>
+      </c>
+      <c r="W97">
+        <v>0.2163472538662254</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.3357972321993088</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2373389302388843</v>
+      </c>
+      <c r="C98">
+        <v>-42.70304923827472</v>
+      </c>
+      <c r="D98">
+        <v>32.38895076172528</v>
+      </c>
+      <c r="E98">
+        <v>50.892</v>
+      </c>
+      <c r="F98">
+        <v>79.392</v>
+      </c>
+      <c r="G98">
+        <v>4.3</v>
+      </c>
+      <c r="H98">
+        <v>54.2</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>14</v>
+      </c>
+      <c r="K98">
+        <v>7.7</v>
+      </c>
+      <c r="L98">
+        <v>6.3</v>
+      </c>
+      <c r="M98">
+        <v>18.9588096</v>
+      </c>
+      <c r="N98">
+        <v>-12.6588096</v>
+      </c>
+      <c r="O98">
+        <v>-3.544466688</v>
+      </c>
+      <c r="P98">
+        <v>-9.114342911999998</v>
+      </c>
+      <c r="Q98">
+        <v>-1.414342911999998</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>0.7355259766492526</v>
+      </c>
+      <c r="T98">
+        <v>15.1462168836794</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.09304381642189181</v>
+      </c>
+      <c r="W98">
+        <v>0.2165811366384522</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.3322993443638994</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2393389302388843</v>
+      </c>
+      <c r="C99">
+        <v>-43.74821180639337</v>
+      </c>
+      <c r="D99">
+        <v>32.17078819360663</v>
+      </c>
+      <c r="E99">
+        <v>51.71899999999999</v>
+      </c>
+      <c r="F99">
+        <v>80.21899999999999</v>
+      </c>
+      <c r="G99">
+        <v>4.3</v>
+      </c>
+      <c r="H99">
+        <v>54.2</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>14</v>
+      </c>
+      <c r="K99">
+        <v>7.7</v>
+      </c>
+      <c r="L99">
+        <v>6.3</v>
+      </c>
+      <c r="M99">
+        <v>19.1562972</v>
+      </c>
+      <c r="N99">
+        <v>-12.8562972</v>
+      </c>
+      <c r="O99">
+        <v>-3.599763216</v>
+      </c>
+      <c r="P99">
+        <v>-9.256533984000001</v>
+      </c>
+      <c r="Q99">
+        <v>-1.556533984000001</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>0.9677679688656704</v>
+      </c>
+      <c r="T99">
+        <v>20.19495584490588</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.09208460181960426</v>
+      </c>
+      <c r="W99">
+        <v>0.2168101970854785</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.3288735779271581</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2413389302388843</v>
+      </c>
+      <c r="C100">
+        <v>-44.79045507861199</v>
+      </c>
+      <c r="D100">
+        <v>31.95554492138802</v>
+      </c>
+      <c r="E100">
+        <v>52.54600000000001</v>
+      </c>
+      <c r="F100">
+        <v>81.04600000000001</v>
+      </c>
+      <c r="G100">
+        <v>4.3</v>
+      </c>
+      <c r="H100">
+        <v>54.2</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>14</v>
+      </c>
+      <c r="K100">
+        <v>7.7</v>
+      </c>
+      <c r="L100">
+        <v>6.3</v>
+      </c>
+      <c r="M100">
+        <v>19.3537848</v>
+      </c>
+      <c r="N100">
+        <v>-13.0537848</v>
+      </c>
+      <c r="O100">
+        <v>-3.655059744000001</v>
+      </c>
+      <c r="P100">
+        <v>-9.398725056000002</v>
+      </c>
+      <c r="Q100">
+        <v>-1.698725056000002</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>1.432251953298505</v>
+      </c>
+      <c r="T100">
+        <v>30.29243376735881</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.09114496302552666</v>
+      </c>
+      <c r="W100">
+        <v>0.2170345828295042</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.3255177250911666</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2433389302388843</v>
+      </c>
+      <c r="C101">
+        <v>-45.82983726139553</v>
+      </c>
+      <c r="D101">
+        <v>31.74316273860448</v>
+      </c>
+      <c r="E101">
+        <v>53.373</v>
+      </c>
+      <c r="F101">
+        <v>81.873</v>
+      </c>
+      <c r="G101">
+        <v>4.3</v>
+      </c>
+      <c r="H101">
+        <v>54.2</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>14</v>
+      </c>
+      <c r="K101">
+        <v>7.7</v>
+      </c>
+      <c r="L101">
+        <v>6.3</v>
+      </c>
+      <c r="M101">
+        <v>19.5512724</v>
+      </c>
+      <c r="N101">
+        <v>-13.2512724</v>
+      </c>
+      <c r="O101">
+        <v>-3.710356272000001</v>
+      </c>
+      <c r="P101">
+        <v>-9.540916128000001</v>
+      </c>
+      <c r="Q101">
+        <v>-1.840916128000001</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>2.825703906597011</v>
+      </c>
+      <c r="T101">
+        <v>60.58486753471763</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.09022430683334962</v>
+      </c>
+      <c r="W101">
+        <v>0.2172544355281961</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.322229667261963</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
